--- a/20260424_Monitoreo-Cumplimiento-Proyectos-PARES.xlsx
+++ b/20260424_Monitoreo-Cumplimiento-Proyectos-PARES.xlsx
@@ -20,7 +20,7 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId16" roundtripDataChecksum="UOexdcw8rRJJ/4fXdGhYUEa68K+spn9yymKhfYDGbCY="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId16" roundtripDataChecksum="ZUbFi6hUymV+8NW6Jovx59SkaU2/GrYRLJTEROA/uvQ="/>
     </ext>
   </extLst>
 </workbook>
@@ -99,7 +99,7 @@
   </commentList>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7mh44+bzKLNxdsfCut2SpPIm7QeSMA=="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7micHj4HpOBScItgJcUplSQAKtKBEg=="/>
     </ext>
   </extLst>
 </comments>
@@ -122,14 +122,14 @@
   </commentList>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7mjRW4EEjyjZPIYDvJLoa1HYpL7CUw=="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7mhRJXCPyGdHISpk/I2idIvZZzbh1A=="/>
     </ext>
   </extLst>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1465" uniqueCount="1158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1467" uniqueCount="1159">
   <si>
     <t xml:space="preserve">CORPORACIÓN BIOCOMERCIO SOSTENIBLE </t>
   </si>
@@ -4341,6 +4341,9 @@
       </rPr>
       <t xml:space="preserve">Se ha construidio una estrategia y plan de trabajo, para organizar y focalizar las acciones de la red, ahora se identifican nuevos comites para fortalecer la RED.  Colocar observaciones de una red vrs dos redes. </t>
     </r>
+  </si>
+  <si>
+    <t>3 Redes administradoras de hombres y mujeres de servicios de agua, para la gestión integrada de los recursos hídricos, capacitadas haciendo incidencia</t>
   </si>
   <si>
     <t xml:space="preserve">2 redes capacitadas en temas de gobernanza y administración, operación y mantenimiento del servicio y de la red.  </t>
@@ -8410,9 +8413,11 @@
       </bottom>
     </border>
     <border>
-      <left style="thin">
+      <right style="thin">
         <color rgb="FF000000"/>
-      </left>
+      </right>
+    </border>
+    <border>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -8421,11 +8426,9 @@
       </bottom>
     </border>
     <border>
-      <right style="thin">
+      <left style="thin">
         <color rgb="FF000000"/>
-      </right>
-    </border>
-    <border>
+      </left>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -8566,7 +8569,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="164">
+  <cellXfs count="163">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -8796,20 +8799,19 @@
       <alignment horizontal="left" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="17" fillId="0" fontId="28" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="18" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="19" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="18" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="19" fillId="0" fontId="28" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="18" fillId="0" fontId="28" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="19" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="18" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="19" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="18" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="19" fillId="0" fontId="28" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="18" fillId="0" fontId="28" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="16" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right"/>
     </xf>
@@ -8827,12 +8829,12 @@
     <xf borderId="0" fillId="0" fontId="28" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="20" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="19" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="7" fillId="0" fontId="28" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="20" fillId="0" fontId="28" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="20" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="19" fillId="0" fontId="28" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="19" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="7" fillId="0" fontId="12" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -8918,7 +8920,7 @@
     <xf borderId="7" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="18" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="20" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="29" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -37746,7 +37748,7 @@
   <sheetData>
     <row r="1" ht="32.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -37796,16 +37798,16 @@
         <v>4</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="H4" s="11" t="s">
         <v>9</v>
@@ -37820,27 +37822,27 @@
         <v>12</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
     </row>
     <row r="5" ht="60.75" customHeight="1">
       <c r="A5" s="17" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="D5" s="18">
         <v>18.0</v>
@@ -37866,26 +37868,26 @@
         <v>0.9428571429</v>
       </c>
       <c r="K5" s="17" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="L5" s="18" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="M5" s="18" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="N5" s="17"/>
       <c r="O5" s="17"/>
     </row>
     <row r="6" ht="60.75" customHeight="1">
       <c r="A6" s="18" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="D6" s="18">
         <v>0.1</v>
@@ -37911,26 +37913,26 @@
         <v>0.5183333333</v>
       </c>
       <c r="K6" s="17" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="L6" s="18" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="M6" s="18" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="N6" s="17"/>
       <c r="O6" s="17"/>
     </row>
     <row r="7" ht="60.75" customHeight="1">
       <c r="A7" s="17" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="D7" s="18">
         <v>1.0</v>
@@ -37956,26 +37958,26 @@
         <v>0.5857142857</v>
       </c>
       <c r="K7" s="17" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="L7" s="18" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="M7" s="18" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="N7" s="17"/>
       <c r="O7" s="17"/>
     </row>
     <row r="8" ht="60.75" customHeight="1">
       <c r="A8" s="17" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="D8" s="18">
         <v>0.1</v>
@@ -38001,26 +38003,26 @@
         <v>0.3</v>
       </c>
       <c r="K8" s="17" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="L8" s="18" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="M8" s="76" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="N8" s="17"/>
       <c r="O8" s="17"/>
     </row>
     <row r="9" ht="60.75" customHeight="1">
       <c r="A9" s="18" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="D9" s="18">
         <v>0.1</v>
@@ -38046,13 +38048,13 @@
         <v>0.1171428571</v>
       </c>
       <c r="K9" s="36" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="L9" s="18" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="M9" s="18" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="N9" s="17"/>
       <c r="O9" s="17"/>
@@ -38104,16 +38106,16 @@
         <v>4</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H12" s="11" t="s">
         <v>9</v>
@@ -38125,30 +38127,30 @@
         <v>301</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="M12" s="11" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="N12" s="11" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="O12" s="11" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
     </row>
     <row r="13" ht="60.75" customHeight="1">
       <c r="A13" s="17" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="D13" s="18">
         <v>0.5</v>
@@ -38174,26 +38176,26 @@
         <v>0.5</v>
       </c>
       <c r="K13" s="17" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="L13" s="18" t="s">
-        <v>911</v>
-      </c>
-      <c r="M13" s="124" t="s">
         <v>912</v>
+      </c>
+      <c r="M13" s="123" t="s">
+        <v>913</v>
       </c>
       <c r="N13" s="17"/>
       <c r="O13" s="17"/>
     </row>
     <row r="14" ht="60.75" customHeight="1">
       <c r="A14" s="17" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="D14" s="18">
         <v>0.1</v>
@@ -38219,26 +38221,26 @@
         <v>0.375</v>
       </c>
       <c r="K14" s="17" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="L14" s="18" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="M14" s="76" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="N14" s="17"/>
       <c r="O14" s="17"/>
     </row>
     <row r="15" ht="60.75" customHeight="1">
       <c r="A15" s="18" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="D15" s="17">
         <v>0.0</v>
@@ -38264,26 +38266,26 @@
         <v>0.5</v>
       </c>
       <c r="K15" s="17" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="L15" s="18" t="s">
-        <v>923</v>
-      </c>
-      <c r="M15" s="112" t="s">
         <v>924</v>
+      </c>
+      <c r="M15" s="111" t="s">
+        <v>925</v>
       </c>
       <c r="N15" s="17"/>
       <c r="O15" s="17"/>
     </row>
     <row r="16" ht="60.75" customHeight="1">
       <c r="A16" s="17" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="D16" s="18">
         <v>0.9</v>
@@ -38309,26 +38311,26 @@
         <v>0.18</v>
       </c>
       <c r="K16" s="17" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="L16" s="18" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="M16" s="18" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="N16" s="17"/>
       <c r="O16" s="17"/>
     </row>
     <row r="17" ht="60.75" customHeight="1">
       <c r="A17" s="33" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="D17" s="17">
         <v>0.0</v>
@@ -38354,26 +38356,26 @@
         <v>0.5384615385</v>
       </c>
       <c r="K17" s="17" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="L17" s="18" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="M17" s="76" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="N17" s="17"/>
       <c r="O17" s="17"/>
     </row>
     <row r="18" ht="60.75" customHeight="1">
       <c r="A18" s="33" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="D18" s="18">
         <v>2.0</v>
@@ -38399,26 +38401,26 @@
         <v>0.7272727273</v>
       </c>
       <c r="K18" s="17" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="L18" s="18" t="s">
-        <v>939</v>
-      </c>
-      <c r="M18" s="112" t="s">
         <v>940</v>
+      </c>
+      <c r="M18" s="111" t="s">
+        <v>941</v>
       </c>
       <c r="N18" s="17"/>
       <c r="O18" s="17"/>
     </row>
     <row r="19" ht="60.75" customHeight="1">
       <c r="A19" s="33" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="D19" s="18">
         <v>0.5</v>
@@ -38444,26 +38446,26 @@
         <v>0.3375806452</v>
       </c>
       <c r="K19" s="17" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="L19" s="18" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="M19" s="76" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="N19" s="17"/>
       <c r="O19" s="17"/>
     </row>
     <row r="20" ht="60.75" customHeight="1">
       <c r="A20" s="33" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="D20" s="18">
         <v>0.5</v>
@@ -38489,23 +38491,23 @@
         <v>0.09090909091</v>
       </c>
       <c r="K20" s="17" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="L20" s="18" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="M20" s="18" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="N20" s="17"/>
       <c r="O20" s="17"/>
     </row>
     <row r="21" ht="60.75" customHeight="1">
       <c r="A21" s="33" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="C21" s="18">
         <v>0.1</v>
@@ -38534,26 +38536,26 @@
         <v>0.9</v>
       </c>
       <c r="K21" s="17" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="L21" s="18" t="s">
-        <v>954</v>
-      </c>
-      <c r="M21" s="124" t="s">
         <v>955</v>
+      </c>
+      <c r="M21" s="123" t="s">
+        <v>956</v>
       </c>
       <c r="N21" s="17"/>
       <c r="O21" s="17"/>
     </row>
     <row r="22" ht="60.75" customHeight="1">
       <c r="A22" s="33" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="D22" s="18">
         <v>0.9</v>
@@ -38579,26 +38581,26 @@
         <v>0.2492857143</v>
       </c>
       <c r="K22" s="17" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="L22" s="18" t="s">
-        <v>959</v>
-      </c>
-      <c r="M22" s="125" t="s">
         <v>960</v>
+      </c>
+      <c r="M22" s="124" t="s">
+        <v>961</v>
       </c>
       <c r="N22" s="17"/>
       <c r="O22" s="17"/>
     </row>
     <row r="23" ht="60.75" customHeight="1">
       <c r="A23" s="33" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="D23" s="17">
         <v>0.0</v>
@@ -38624,26 +38626,26 @@
         <v>0.2</v>
       </c>
       <c r="K23" s="17" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="L23" s="18" t="s">
-        <v>964</v>
-      </c>
-      <c r="M23" s="124" t="s">
         <v>965</v>
+      </c>
+      <c r="M23" s="123" t="s">
+        <v>966</v>
       </c>
       <c r="N23" s="17"/>
       <c r="O23" s="17"/>
     </row>
     <row r="24" ht="60.75" customHeight="1">
       <c r="A24" s="33" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="D24" s="18">
         <v>0.1</v>
@@ -38669,26 +38671,26 @@
         <v>0.6833333333</v>
       </c>
       <c r="K24" s="17" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="L24" s="18" t="s">
-        <v>969</v>
-      </c>
-      <c r="M24" s="124" t="s">
         <v>970</v>
+      </c>
+      <c r="M24" s="123" t="s">
+        <v>971</v>
       </c>
       <c r="N24" s="17"/>
       <c r="O24" s="17"/>
     </row>
     <row r="25" ht="60.75" customHeight="1">
       <c r="A25" s="33" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="D25" s="17">
         <v>0.0</v>
@@ -38714,83 +38716,83 @@
         <v>0.003846153846</v>
       </c>
       <c r="K25" s="17" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="L25" s="18" t="s">
-        <v>974</v>
-      </c>
-      <c r="M25" s="112" t="s">
         <v>975</v>
+      </c>
+      <c r="M25" s="111" t="s">
+        <v>976</v>
       </c>
       <c r="N25" s="17"/>
       <c r="O25" s="17"/>
     </row>
     <row r="26" ht="14.25" customHeight="1">
-      <c r="A26" s="126"/>
-      <c r="B26" s="126"/>
-      <c r="C26" s="126"/>
-      <c r="D26" s="126"/>
-      <c r="E26" s="126"/>
-      <c r="F26" s="126"/>
-      <c r="G26" s="126"/>
-      <c r="H26" s="126"/>
-      <c r="I26" s="126"/>
-      <c r="J26" s="126"/>
-      <c r="K26" s="126"/>
-      <c r="L26" s="126"/>
-      <c r="N26" s="126"/>
-      <c r="O26" s="126"/>
+      <c r="A26" s="125"/>
+      <c r="B26" s="125"/>
+      <c r="C26" s="125"/>
+      <c r="D26" s="125"/>
+      <c r="E26" s="125"/>
+      <c r="F26" s="125"/>
+      <c r="G26" s="125"/>
+      <c r="H26" s="125"/>
+      <c r="I26" s="125"/>
+      <c r="J26" s="125"/>
+      <c r="K26" s="125"/>
+      <c r="L26" s="125"/>
+      <c r="N26" s="125"/>
+      <c r="O26" s="125"/>
     </row>
     <row r="27" ht="14.25" customHeight="1">
-      <c r="A27" s="126"/>
-      <c r="B27" s="126"/>
-      <c r="C27" s="126"/>
-      <c r="D27" s="126"/>
-      <c r="E27" s="126"/>
-      <c r="F27" s="126"/>
-      <c r="G27" s="126"/>
-      <c r="H27" s="126"/>
-      <c r="I27" s="126"/>
-      <c r="J27" s="126"/>
-      <c r="K27" s="126"/>
-      <c r="L27" s="126"/>
-      <c r="M27" s="126"/>
-      <c r="N27" s="126"/>
-      <c r="O27" s="126"/>
+      <c r="A27" s="125"/>
+      <c r="B27" s="125"/>
+      <c r="C27" s="125"/>
+      <c r="D27" s="125"/>
+      <c r="E27" s="125"/>
+      <c r="F27" s="125"/>
+      <c r="G27" s="125"/>
+      <c r="H27" s="125"/>
+      <c r="I27" s="125"/>
+      <c r="J27" s="125"/>
+      <c r="K27" s="125"/>
+      <c r="L27" s="125"/>
+      <c r="M27" s="125"/>
+      <c r="N27" s="125"/>
+      <c r="O27" s="125"/>
     </row>
     <row r="28" ht="14.25" customHeight="1">
-      <c r="A28" s="126"/>
-      <c r="B28" s="126"/>
-      <c r="C28" s="126"/>
-      <c r="D28" s="126"/>
-      <c r="E28" s="126"/>
-      <c r="F28" s="126"/>
-      <c r="G28" s="126"/>
-      <c r="H28" s="126"/>
-      <c r="I28" s="126"/>
-      <c r="J28" s="126"/>
-      <c r="K28" s="126"/>
-      <c r="L28" s="126"/>
-      <c r="M28" s="126"/>
-      <c r="N28" s="126"/>
-      <c r="O28" s="126"/>
+      <c r="A28" s="125"/>
+      <c r="B28" s="125"/>
+      <c r="C28" s="125"/>
+      <c r="D28" s="125"/>
+      <c r="E28" s="125"/>
+      <c r="F28" s="125"/>
+      <c r="G28" s="125"/>
+      <c r="H28" s="125"/>
+      <c r="I28" s="125"/>
+      <c r="J28" s="125"/>
+      <c r="K28" s="125"/>
+      <c r="L28" s="125"/>
+      <c r="M28" s="125"/>
+      <c r="N28" s="125"/>
+      <c r="O28" s="125"/>
     </row>
     <row r="29" ht="14.25" customHeight="1">
-      <c r="A29" s="126"/>
-      <c r="B29" s="126"/>
-      <c r="C29" s="126"/>
-      <c r="D29" s="126"/>
-      <c r="E29" s="126"/>
-      <c r="F29" s="126"/>
-      <c r="G29" s="126"/>
-      <c r="H29" s="126"/>
-      <c r="I29" s="126"/>
-      <c r="J29" s="126"/>
-      <c r="K29" s="126"/>
-      <c r="L29" s="126"/>
-      <c r="M29" s="126"/>
-      <c r="N29" s="126"/>
-      <c r="O29" s="126"/>
+      <c r="A29" s="125"/>
+      <c r="B29" s="125"/>
+      <c r="C29" s="125"/>
+      <c r="D29" s="125"/>
+      <c r="E29" s="125"/>
+      <c r="F29" s="125"/>
+      <c r="G29" s="125"/>
+      <c r="H29" s="125"/>
+      <c r="I29" s="125"/>
+      <c r="J29" s="125"/>
+      <c r="K29" s="125"/>
+      <c r="L29" s="125"/>
+      <c r="M29" s="125"/>
+      <c r="N29" s="125"/>
+      <c r="O29" s="125"/>
     </row>
     <row r="30" ht="14.25" customHeight="1">
       <c r="A30" s="5"/>
@@ -41743,7 +41745,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -41790,16 +41792,16 @@
         <v>4</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H4" s="11" t="s">
         <v>9</v>
@@ -41807,31 +41809,31 @@
       <c r="I4" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="127" t="s">
+      <c r="J4" s="126" t="s">
         <v>301</v>
       </c>
       <c r="K4" s="11" t="s">
         <v>12</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
     </row>
     <row r="5" ht="64.5" customHeight="1">
       <c r="A5" s="32" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="C5" s="17">
         <v>0.0</v>
@@ -41860,26 +41862,26 @@
         <v>0.65</v>
       </c>
       <c r="K5" s="18" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="L5" s="18" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="M5" s="18" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="N5" s="17"/>
       <c r="O5" s="17"/>
     </row>
     <row r="6" ht="64.5" customHeight="1">
       <c r="A6" s="18" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="D6" s="17">
         <v>0.0</v>
@@ -41905,23 +41907,23 @@
         <v>0</v>
       </c>
       <c r="K6" s="18" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="L6" s="18" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="M6" s="18" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="N6" s="17"/>
       <c r="O6" s="17"/>
     </row>
     <row r="7" ht="64.5" customHeight="1">
       <c r="A7" s="18" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="C7" s="17">
         <v>0.0</v>
@@ -41950,26 +41952,26 @@
         <v>0.25</v>
       </c>
       <c r="K7" s="18" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="L7" s="18" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="M7" s="18" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="N7" s="17"/>
       <c r="O7" s="17"/>
     </row>
     <row r="8" ht="64.5" customHeight="1">
-      <c r="A8" s="105" t="s">
-        <v>1001</v>
+      <c r="A8" s="104" t="s">
+        <v>1002</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="D8" s="18">
         <v>0.0</v>
@@ -41994,26 +41996,26 @@
         <v>0</v>
       </c>
       <c r="K8" s="18" t="s">
-        <v>1004</v>
-      </c>
-      <c r="L8" s="105" t="s">
         <v>1005</v>
       </c>
-      <c r="M8" s="105" t="s">
+      <c r="L8" s="104" t="s">
         <v>1006</v>
+      </c>
+      <c r="M8" s="104" t="s">
+        <v>1007</v>
       </c>
       <c r="N8" s="17"/>
       <c r="O8" s="17"/>
     </row>
     <row r="9" ht="64.5" customHeight="1">
-      <c r="A9" s="105" t="s">
-        <v>1001</v>
+      <c r="A9" s="104" t="s">
+        <v>1002</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="D9" s="73">
         <v>2.0</v>
@@ -42039,26 +42041,26 @@
         <v>1</v>
       </c>
       <c r="K9" s="18" t="s">
-        <v>1009</v>
-      </c>
-      <c r="L9" s="105" t="s">
         <v>1010</v>
       </c>
-      <c r="M9" s="105" t="s">
-        <v>1006</v>
+      <c r="L9" s="104" t="s">
+        <v>1011</v>
+      </c>
+      <c r="M9" s="104" t="s">
+        <v>1007</v>
       </c>
       <c r="N9" s="17"/>
       <c r="O9" s="17"/>
     </row>
     <row r="10" ht="64.5" customHeight="1">
       <c r="A10" s="38" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="D10" s="17">
         <v>0.0</v>
@@ -42084,24 +42086,24 @@
         <v>0.1428571429</v>
       </c>
       <c r="K10" s="18" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="L10" s="17"/>
       <c r="M10" s="18" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="N10" s="17"/>
       <c r="O10" s="17"/>
     </row>
     <row r="11" ht="64.5" customHeight="1">
       <c r="A11" s="38" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="D11" s="17">
         <v>0.0</v>
@@ -42127,21 +42129,21 @@
         <v>0</v>
       </c>
       <c r="K11" s="18" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="L11" s="17"/>
       <c r="M11" s="18" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="N11" s="17"/>
       <c r="O11" s="17"/>
     </row>
     <row r="12" ht="64.5" customHeight="1">
       <c r="A12" s="17" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="C12" s="18">
         <v>0.0</v>
@@ -42170,11 +42172,11 @@
         <v>0.3666666667</v>
       </c>
       <c r="K12" s="17" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="L12" s="17"/>
       <c r="M12" s="18" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="N12" s="17"/>
       <c r="O12" s="17"/>
@@ -42209,16 +42211,16 @@
         <v>4</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="H14" s="11" t="s">
         <v>9</v>
@@ -42230,27 +42232,27 @@
         <v>301</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="L14" s="11" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="M14" s="11" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="N14" s="11" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="O14" s="11" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="15" ht="64.5" customHeight="1">
-      <c r="A15" s="128" t="s">
-        <v>1032</v>
+      <c r="A15" s="127" t="s">
+        <v>1033</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="C15" s="17">
         <v>0.0</v>
@@ -42279,24 +42281,24 @@
         <v>0</v>
       </c>
       <c r="K15" s="17" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="L15" s="18" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="M15" s="17"/>
       <c r="N15" s="17"/>
       <c r="O15" s="17"/>
     </row>
     <row r="16" ht="64.5" customHeight="1">
-      <c r="A16" s="105" t="s">
-        <v>1036</v>
+      <c r="A16" s="104" t="s">
+        <v>1037</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>1037</v>
-      </c>
-      <c r="C16" s="105" t="s">
         <v>1038</v>
+      </c>
+      <c r="C16" s="104" t="s">
+        <v>1039</v>
       </c>
       <c r="D16" s="18">
         <v>0.0</v>
@@ -42321,27 +42323,27 @@
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="K16" s="105" t="s">
-        <v>1039</v>
-      </c>
-      <c r="L16" s="105" t="s">
-        <v>1035</v>
-      </c>
-      <c r="M16" s="105" t="s">
+      <c r="K16" s="104" t="s">
         <v>1040</v>
+      </c>
+      <c r="L16" s="104" t="s">
+        <v>1036</v>
+      </c>
+      <c r="M16" s="104" t="s">
+        <v>1041</v>
       </c>
       <c r="N16" s="17"/>
       <c r="O16" s="17"/>
     </row>
     <row r="17" ht="64.5" customHeight="1">
-      <c r="A17" s="105" t="s">
-        <v>1036</v>
+      <c r="A17" s="104" t="s">
+        <v>1037</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>1041</v>
-      </c>
-      <c r="C17" s="105" t="s">
-        <v>1038</v>
+        <v>1042</v>
+      </c>
+      <c r="C17" s="104" t="s">
+        <v>1039</v>
       </c>
       <c r="D17" s="18">
         <v>0.0</v>
@@ -42362,31 +42364,31 @@
       <c r="I17" s="70">
         <v>0.7</v>
       </c>
-      <c r="J17" s="129">
+      <c r="J17" s="128">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K17" s="105" t="s">
-        <v>1042</v>
-      </c>
-      <c r="L17" s="105" t="s">
-        <v>1035</v>
-      </c>
-      <c r="M17" s="105" t="s">
-        <v>1040</v>
+      <c r="K17" s="104" t="s">
+        <v>1043</v>
+      </c>
+      <c r="L17" s="104" t="s">
+        <v>1036</v>
+      </c>
+      <c r="M17" s="104" t="s">
+        <v>1041</v>
       </c>
       <c r="N17" s="17"/>
       <c r="O17" s="17"/>
     </row>
     <row r="18" ht="64.5" customHeight="1">
       <c r="A18" s="18" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="D18" s="18">
         <v>1300.0</v>
@@ -42412,26 +42414,26 @@
         <v>1.375</v>
       </c>
       <c r="K18" s="18" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="L18" s="18" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="M18" s="18" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="N18" s="17"/>
       <c r="O18" s="17"/>
     </row>
     <row r="19" ht="64.5" customHeight="1">
       <c r="A19" s="18" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="D19" s="18">
         <v>750.0</v>
@@ -42457,26 +42459,26 @@
         <v>0.75</v>
       </c>
       <c r="K19" s="18" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="L19" s="18" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="M19" s="18" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="N19" s="17"/>
       <c r="O19" s="17"/>
     </row>
     <row r="20" ht="64.5" customHeight="1">
       <c r="A20" s="18" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="D20" s="18">
         <v>0.0</v>
@@ -42487,7 +42489,7 @@
       <c r="F20" s="18">
         <v>0.0</v>
       </c>
-      <c r="G20" s="130">
+      <c r="G20" s="129">
         <v>0.0</v>
       </c>
       <c r="H20" s="17">
@@ -42502,37 +42504,37 @@
         <v>0.5</v>
       </c>
       <c r="K20" s="18" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="L20" s="18" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="M20" s="18" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="N20" s="17"/>
       <c r="O20" s="17"/>
     </row>
     <row r="21" ht="64.5" customHeight="1">
       <c r="A21" s="18" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>1061</v>
-      </c>
-      <c r="D21" s="131">
+        <v>1062</v>
+      </c>
+      <c r="D21" s="130">
         <v>0.82</v>
       </c>
-      <c r="E21" s="131">
+      <c r="E21" s="130">
         <v>0.1</v>
       </c>
-      <c r="F21" s="132">
+      <c r="F21" s="131">
         <v>0.0</v>
       </c>
-      <c r="G21" s="132">
+      <c r="G21" s="131">
         <v>0.0</v>
       </c>
       <c r="H21" s="58">
@@ -42542,41 +42544,41 @@
       <c r="I21" s="19">
         <v>0.15</v>
       </c>
-      <c r="J21" s="106">
+      <c r="J21" s="105">
         <v>0.82</v>
       </c>
       <c r="K21" s="18" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="L21" s="18" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="M21" s="18" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="N21" s="17"/>
       <c r="O21" s="17"/>
     </row>
     <row r="22" ht="64.5" customHeight="1">
       <c r="A22" s="18" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="C22" s="18">
         <v>0.0</v>
       </c>
-      <c r="D22" s="132">
+      <c r="D22" s="131">
         <v>0.0</v>
       </c>
-      <c r="E22" s="131">
+      <c r="E22" s="130">
         <v>0.08</v>
       </c>
-      <c r="F22" s="132">
+      <c r="F22" s="131">
         <v>0.0</v>
       </c>
-      <c r="G22" s="132">
+      <c r="G22" s="131">
         <v>0.0</v>
       </c>
       <c r="H22" s="58">
@@ -42591,37 +42593,37 @@
         <v>0.2666666667</v>
       </c>
       <c r="K22" s="18" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="L22" s="18" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="M22" s="18" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="N22" s="17"/>
       <c r="O22" s="17"/>
     </row>
     <row r="23" ht="64.5" customHeight="1">
       <c r="A23" s="18" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>1070</v>
-      </c>
-      <c r="D23" s="132">
+        <v>1071</v>
+      </c>
+      <c r="D23" s="131">
         <v>0.0</v>
       </c>
-      <c r="E23" s="132">
+      <c r="E23" s="131">
         <v>0.0</v>
       </c>
-      <c r="F23" s="132">
+      <c r="F23" s="131">
         <v>0.0</v>
       </c>
-      <c r="G23" s="130">
+      <c r="G23" s="129">
         <v>0.0</v>
       </c>
       <c r="H23" s="17">
@@ -42636,35 +42638,35 @@
         <v>0</v>
       </c>
       <c r="K23" s="18" t="s">
-        <v>1071</v>
-      </c>
-      <c r="L23" s="133"/>
+        <v>1072</v>
+      </c>
+      <c r="L23" s="132"/>
       <c r="M23" s="18" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="N23" s="17"/>
       <c r="O23" s="17"/>
     </row>
     <row r="24" ht="64.5" customHeight="1">
       <c r="A24" s="18" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="C24" s="18">
         <v>0.0</v>
       </c>
-      <c r="D24" s="132">
+      <c r="D24" s="131">
         <v>0.0</v>
       </c>
-      <c r="E24" s="132">
+      <c r="E24" s="131">
         <v>0.0</v>
       </c>
-      <c r="F24" s="132">
+      <c r="F24" s="131">
         <v>0.0</v>
       </c>
-      <c r="G24" s="130">
+      <c r="G24" s="129">
         <v>0.0</v>
       </c>
       <c r="H24" s="18">
@@ -42678,167 +42680,167 @@
         <v>0</v>
       </c>
       <c r="K24" s="18" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="L24" s="18"/>
       <c r="M24" s="18" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="N24" s="18"/>
       <c r="O24" s="18"/>
     </row>
     <row r="25">
-      <c r="A25" s="126"/>
-      <c r="B25" s="126"/>
-      <c r="C25" s="126"/>
-      <c r="D25" s="126"/>
-      <c r="E25" s="126"/>
-      <c r="F25" s="126"/>
-      <c r="G25" s="126"/>
-      <c r="H25" s="126"/>
-      <c r="I25" s="126"/>
-      <c r="J25" s="126"/>
-      <c r="K25" s="126"/>
-      <c r="L25" s="126"/>
-      <c r="M25" s="126"/>
-      <c r="N25" s="126"/>
-      <c r="O25" s="126"/>
+      <c r="A25" s="125"/>
+      <c r="B25" s="125"/>
+      <c r="C25" s="125"/>
+      <c r="D25" s="125"/>
+      <c r="E25" s="125"/>
+      <c r="F25" s="125"/>
+      <c r="G25" s="125"/>
+      <c r="H25" s="125"/>
+      <c r="I25" s="125"/>
+      <c r="J25" s="125"/>
+      <c r="K25" s="125"/>
+      <c r="L25" s="125"/>
+      <c r="M25" s="125"/>
+      <c r="N25" s="125"/>
+      <c r="O25" s="125"/>
     </row>
     <row r="26">
-      <c r="A26" s="126"/>
-      <c r="B26" s="126"/>
-      <c r="C26" s="126"/>
-      <c r="D26" s="126"/>
-      <c r="E26" s="126"/>
-      <c r="F26" s="126"/>
-      <c r="G26" s="126"/>
-      <c r="H26" s="126"/>
-      <c r="I26" s="126"/>
-      <c r="J26" s="126"/>
-      <c r="K26" s="126"/>
-      <c r="L26" s="126"/>
-      <c r="M26" s="126"/>
-      <c r="N26" s="126"/>
-      <c r="O26" s="126"/>
+      <c r="A26" s="125"/>
+      <c r="B26" s="125"/>
+      <c r="C26" s="125"/>
+      <c r="D26" s="125"/>
+      <c r="E26" s="125"/>
+      <c r="F26" s="125"/>
+      <c r="G26" s="125"/>
+      <c r="H26" s="125"/>
+      <c r="I26" s="125"/>
+      <c r="J26" s="125"/>
+      <c r="K26" s="125"/>
+      <c r="L26" s="125"/>
+      <c r="M26" s="125"/>
+      <c r="N26" s="125"/>
+      <c r="O26" s="125"/>
     </row>
     <row r="27">
-      <c r="A27" s="126"/>
-      <c r="B27" s="126"/>
-      <c r="C27" s="126"/>
-      <c r="D27" s="126"/>
-      <c r="E27" s="126"/>
-      <c r="F27" s="126"/>
-      <c r="G27" s="126"/>
-      <c r="H27" s="126"/>
-      <c r="I27" s="126"/>
-      <c r="J27" s="126"/>
-      <c r="K27" s="126"/>
-      <c r="L27" s="126"/>
-      <c r="M27" s="126"/>
-      <c r="N27" s="126"/>
-      <c r="O27" s="126"/>
+      <c r="A27" s="125"/>
+      <c r="B27" s="125"/>
+      <c r="C27" s="125"/>
+      <c r="D27" s="125"/>
+      <c r="E27" s="125"/>
+      <c r="F27" s="125"/>
+      <c r="G27" s="125"/>
+      <c r="H27" s="125"/>
+      <c r="I27" s="125"/>
+      <c r="J27" s="125"/>
+      <c r="K27" s="125"/>
+      <c r="L27" s="125"/>
+      <c r="M27" s="125"/>
+      <c r="N27" s="125"/>
+      <c r="O27" s="125"/>
     </row>
     <row r="28">
-      <c r="A28" s="126"/>
-      <c r="B28" s="126"/>
-      <c r="C28" s="126"/>
-      <c r="D28" s="126"/>
-      <c r="E28" s="126"/>
-      <c r="F28" s="126"/>
-      <c r="G28" s="126"/>
-      <c r="H28" s="126"/>
-      <c r="I28" s="126"/>
-      <c r="J28" s="126"/>
-      <c r="K28" s="126"/>
-      <c r="L28" s="126"/>
-      <c r="M28" s="126"/>
-      <c r="N28" s="126"/>
-      <c r="O28" s="126"/>
+      <c r="A28" s="125"/>
+      <c r="B28" s="125"/>
+      <c r="C28" s="125"/>
+      <c r="D28" s="125"/>
+      <c r="E28" s="125"/>
+      <c r="F28" s="125"/>
+      <c r="G28" s="125"/>
+      <c r="H28" s="125"/>
+      <c r="I28" s="125"/>
+      <c r="J28" s="125"/>
+      <c r="K28" s="125"/>
+      <c r="L28" s="125"/>
+      <c r="M28" s="125"/>
+      <c r="N28" s="125"/>
+      <c r="O28" s="125"/>
     </row>
     <row r="29">
-      <c r="A29" s="126"/>
-      <c r="B29" s="126"/>
-      <c r="C29" s="126"/>
-      <c r="D29" s="126"/>
-      <c r="E29" s="126"/>
-      <c r="F29" s="126"/>
-      <c r="G29" s="126"/>
-      <c r="H29" s="126"/>
-      <c r="I29" s="126"/>
-      <c r="J29" s="126"/>
-      <c r="K29" s="126"/>
-      <c r="L29" s="126"/>
-      <c r="M29" s="126"/>
-      <c r="N29" s="126"/>
-      <c r="O29" s="126"/>
+      <c r="A29" s="125"/>
+      <c r="B29" s="125"/>
+      <c r="C29" s="125"/>
+      <c r="D29" s="125"/>
+      <c r="E29" s="125"/>
+      <c r="F29" s="125"/>
+      <c r="G29" s="125"/>
+      <c r="H29" s="125"/>
+      <c r="I29" s="125"/>
+      <c r="J29" s="125"/>
+      <c r="K29" s="125"/>
+      <c r="L29" s="125"/>
+      <c r="M29" s="125"/>
+      <c r="N29" s="125"/>
+      <c r="O29" s="125"/>
     </row>
     <row r="30">
-      <c r="A30" s="126"/>
-      <c r="B30" s="126"/>
-      <c r="C30" s="126"/>
-      <c r="D30" s="126"/>
-      <c r="E30" s="126"/>
-      <c r="F30" s="126"/>
-      <c r="G30" s="126"/>
-      <c r="H30" s="126"/>
-      <c r="I30" s="126"/>
-      <c r="J30" s="126"/>
-      <c r="K30" s="126"/>
-      <c r="L30" s="126"/>
-      <c r="M30" s="126"/>
-      <c r="N30" s="126"/>
-      <c r="O30" s="126"/>
+      <c r="A30" s="125"/>
+      <c r="B30" s="125"/>
+      <c r="C30" s="125"/>
+      <c r="D30" s="125"/>
+      <c r="E30" s="125"/>
+      <c r="F30" s="125"/>
+      <c r="G30" s="125"/>
+      <c r="H30" s="125"/>
+      <c r="I30" s="125"/>
+      <c r="J30" s="125"/>
+      <c r="K30" s="125"/>
+      <c r="L30" s="125"/>
+      <c r="M30" s="125"/>
+      <c r="N30" s="125"/>
+      <c r="O30" s="125"/>
     </row>
     <row r="31">
-      <c r="A31" s="126"/>
-      <c r="B31" s="126"/>
-      <c r="C31" s="126"/>
-      <c r="D31" s="126"/>
-      <c r="E31" s="126"/>
-      <c r="F31" s="126"/>
-      <c r="G31" s="126"/>
-      <c r="H31" s="126"/>
-      <c r="I31" s="126"/>
-      <c r="J31" s="126"/>
-      <c r="K31" s="126"/>
-      <c r="L31" s="126"/>
-      <c r="M31" s="126"/>
-      <c r="N31" s="126"/>
-      <c r="O31" s="126"/>
+      <c r="A31" s="125"/>
+      <c r="B31" s="125"/>
+      <c r="C31" s="125"/>
+      <c r="D31" s="125"/>
+      <c r="E31" s="125"/>
+      <c r="F31" s="125"/>
+      <c r="G31" s="125"/>
+      <c r="H31" s="125"/>
+      <c r="I31" s="125"/>
+      <c r="J31" s="125"/>
+      <c r="K31" s="125"/>
+      <c r="L31" s="125"/>
+      <c r="M31" s="125"/>
+      <c r="N31" s="125"/>
+      <c r="O31" s="125"/>
     </row>
     <row r="32">
-      <c r="A32" s="126"/>
-      <c r="B32" s="126"/>
-      <c r="C32" s="126"/>
-      <c r="D32" s="126"/>
-      <c r="E32" s="126"/>
-      <c r="F32" s="126"/>
-      <c r="G32" s="126"/>
-      <c r="H32" s="126"/>
-      <c r="I32" s="126"/>
-      <c r="J32" s="126"/>
-      <c r="K32" s="126"/>
-      <c r="L32" s="126"/>
-      <c r="M32" s="126"/>
-      <c r="N32" s="126"/>
-      <c r="O32" s="126"/>
+      <c r="A32" s="125"/>
+      <c r="B32" s="125"/>
+      <c r="C32" s="125"/>
+      <c r="D32" s="125"/>
+      <c r="E32" s="125"/>
+      <c r="F32" s="125"/>
+      <c r="G32" s="125"/>
+      <c r="H32" s="125"/>
+      <c r="I32" s="125"/>
+      <c r="J32" s="125"/>
+      <c r="K32" s="125"/>
+      <c r="L32" s="125"/>
+      <c r="M32" s="125"/>
+      <c r="N32" s="125"/>
+      <c r="O32" s="125"/>
     </row>
     <row r="33">
-      <c r="A33" s="126"/>
-      <c r="B33" s="126"/>
-      <c r="C33" s="126"/>
-      <c r="D33" s="126"/>
-      <c r="E33" s="126"/>
-      <c r="F33" s="126"/>
-      <c r="G33" s="126"/>
-      <c r="H33" s="126"/>
-      <c r="I33" s="126"/>
-      <c r="J33" s="126"/>
-      <c r="K33" s="126"/>
-      <c r="L33" s="126"/>
-      <c r="M33" s="126"/>
-      <c r="N33" s="126"/>
-      <c r="O33" s="126"/>
+      <c r="A33" s="125"/>
+      <c r="B33" s="125"/>
+      <c r="C33" s="125"/>
+      <c r="D33" s="125"/>
+      <c r="E33" s="125"/>
+      <c r="F33" s="125"/>
+      <c r="G33" s="125"/>
+      <c r="H33" s="125"/>
+      <c r="I33" s="125"/>
+      <c r="J33" s="125"/>
+      <c r="K33" s="125"/>
+      <c r="L33" s="125"/>
+      <c r="M33" s="125"/>
+      <c r="N33" s="125"/>
+      <c r="O33" s="125"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -42873,8 +42875,8 @@
   </cols>
   <sheetData>
     <row r="1" ht="32.25" customHeight="1">
-      <c r="A1" s="134" t="s">
-        <v>1077</v>
+      <c r="A1" s="133" t="s">
+        <v>1078</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -42893,23 +42895,23 @@
     </row>
     <row r="2" ht="14.25" customHeight="1"/>
     <row r="3" ht="58.5" customHeight="1">
-      <c r="A3" s="135" t="s">
+      <c r="A3" s="134" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="136"/>
-      <c r="C3" s="136"/>
-      <c r="D3" s="136"/>
-      <c r="E3" s="136"/>
-      <c r="F3" s="136"/>
-      <c r="G3" s="136"/>
-      <c r="H3" s="137"/>
-      <c r="I3" s="137"/>
-      <c r="J3" s="137"/>
-      <c r="K3" s="138"/>
-      <c r="L3" s="139"/>
-      <c r="M3" s="139"/>
-      <c r="N3" s="139"/>
-      <c r="O3" s="140"/>
+      <c r="B3" s="135"/>
+      <c r="C3" s="135"/>
+      <c r="D3" s="135"/>
+      <c r="E3" s="135"/>
+      <c r="F3" s="135"/>
+      <c r="G3" s="135"/>
+      <c r="H3" s="136"/>
+      <c r="I3" s="136"/>
+      <c r="J3" s="136"/>
+      <c r="K3" s="137"/>
+      <c r="L3" s="138"/>
+      <c r="M3" s="138"/>
+      <c r="N3" s="138"/>
+      <c r="O3" s="139"/>
     </row>
     <row r="4" ht="58.5" customHeight="1">
       <c r="A4" s="11" t="s">
@@ -42922,16 +42924,16 @@
         <v>4</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="H4" s="11" t="s">
         <v>9</v>
@@ -42945,134 +42947,134 @@
       <c r="K4" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="L4" s="141" t="s">
-        <v>1082</v>
-      </c>
-      <c r="M4" s="142" t="s">
+      <c r="L4" s="140" t="s">
         <v>1083</v>
       </c>
-      <c r="N4" s="142" t="s">
+      <c r="M4" s="141" t="s">
         <v>1084</v>
       </c>
-      <c r="O4" s="143" t="s">
+      <c r="N4" s="141" t="s">
         <v>1085</v>
+      </c>
+      <c r="O4" s="142" t="s">
+        <v>1086</v>
       </c>
     </row>
     <row r="5" ht="58.5" customHeight="1">
       <c r="A5" s="16" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="C5" s="63" t="s">
-        <v>1088</v>
-      </c>
-      <c r="D5" s="144">
+        <v>1089</v>
+      </c>
+      <c r="D5" s="143">
         <v>0.1</v>
       </c>
-      <c r="E5" s="144">
+      <c r="E5" s="143">
         <v>0.65</v>
       </c>
       <c r="F5" s="63"/>
       <c r="G5" s="63"/>
-      <c r="H5" s="144">
+      <c r="H5" s="143">
         <f>SUM(D5:G5)</f>
         <v>0.75</v>
       </c>
-      <c r="I5" s="144">
+      <c r="I5" s="143">
         <v>0.7</v>
       </c>
-      <c r="J5" s="145">
+      <c r="J5" s="144">
         <f>H5/I5</f>
         <v>1.071428571</v>
       </c>
-      <c r="K5" s="146" t="s">
-        <v>1089</v>
-      </c>
-      <c r="L5" s="147" t="s">
+      <c r="K5" s="145" t="s">
         <v>1090</v>
       </c>
-      <c r="M5" s="146" t="s">
+      <c r="L5" s="146" t="s">
         <v>1091</v>
+      </c>
+      <c r="M5" s="145" t="s">
+        <v>1092</v>
       </c>
       <c r="N5" s="63"/>
       <c r="O5" s="63"/>
     </row>
     <row r="6" ht="58.5" customHeight="1">
       <c r="A6" s="16" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>1093</v>
-      </c>
-      <c r="C6" s="146" t="s">
         <v>1094</v>
       </c>
-      <c r="D6" s="148" t="s">
+      <c r="C6" s="145" t="s">
         <v>1095</v>
       </c>
-      <c r="E6" s="146">
+      <c r="D6" s="147" t="s">
+        <v>1096</v>
+      </c>
+      <c r="E6" s="145">
         <v>1.0</v>
       </c>
       <c r="F6" s="63"/>
       <c r="G6" s="63"/>
-      <c r="H6" s="146">
+      <c r="H6" s="145">
         <v>2.0</v>
       </c>
-      <c r="I6" s="146">
+      <c r="I6" s="145">
         <v>2.0</v>
       </c>
-      <c r="J6" s="149">
+      <c r="J6" s="148">
         <v>0.51</v>
       </c>
-      <c r="K6" s="146" t="s">
-        <v>1096</v>
-      </c>
-      <c r="L6" s="147" t="s">
+      <c r="K6" s="145" t="s">
         <v>1097</v>
       </c>
-      <c r="M6" s="146" t="s">
+      <c r="L6" s="146" t="s">
         <v>1098</v>
+      </c>
+      <c r="M6" s="145" t="s">
+        <v>1099</v>
       </c>
       <c r="N6" s="63"/>
       <c r="O6" s="63"/>
     </row>
     <row r="7" ht="58.5" customHeight="1">
-      <c r="A7" s="150"/>
-      <c r="B7" s="150"/>
-      <c r="C7" s="126"/>
-      <c r="D7" s="126"/>
-      <c r="E7" s="126"/>
-      <c r="F7" s="126"/>
-      <c r="G7" s="126"/>
-      <c r="H7" s="126"/>
-      <c r="I7" s="126"/>
-      <c r="J7" s="126"/>
-      <c r="K7" s="126"/>
-      <c r="L7" s="126"/>
-      <c r="M7" s="126"/>
-      <c r="N7" s="126"/>
-      <c r="O7" s="126"/>
+      <c r="A7" s="149"/>
+      <c r="B7" s="149"/>
+      <c r="C7" s="125"/>
+      <c r="D7" s="125"/>
+      <c r="E7" s="125"/>
+      <c r="F7" s="125"/>
+      <c r="G7" s="125"/>
+      <c r="H7" s="125"/>
+      <c r="I7" s="125"/>
+      <c r="J7" s="125"/>
+      <c r="K7" s="125"/>
+      <c r="L7" s="125"/>
+      <c r="M7" s="125"/>
+      <c r="N7" s="125"/>
+      <c r="O7" s="125"/>
     </row>
     <row r="8" ht="58.5" customHeight="1">
-      <c r="A8" s="151" t="s">
+      <c r="A8" s="150" t="s">
         <v>53</v>
       </c>
-      <c r="B8" s="152"/>
-      <c r="C8" s="152"/>
-      <c r="D8" s="152"/>
-      <c r="E8" s="152"/>
-      <c r="F8" s="152"/>
-      <c r="G8" s="152"/>
-      <c r="H8" s="153"/>
-      <c r="I8" s="153"/>
-      <c r="J8" s="153"/>
-      <c r="K8" s="154"/>
-      <c r="L8" s="155"/>
-      <c r="M8" s="155"/>
-      <c r="N8" s="155"/>
-      <c r="O8" s="156"/>
+      <c r="B8" s="151"/>
+      <c r="C8" s="151"/>
+      <c r="D8" s="151"/>
+      <c r="E8" s="151"/>
+      <c r="F8" s="151"/>
+      <c r="G8" s="151"/>
+      <c r="H8" s="152"/>
+      <c r="I8" s="152"/>
+      <c r="J8" s="152"/>
+      <c r="K8" s="153"/>
+      <c r="L8" s="154"/>
+      <c r="M8" s="154"/>
+      <c r="N8" s="154"/>
+      <c r="O8" s="155"/>
     </row>
     <row r="9" ht="58.5" customHeight="1">
       <c r="A9" s="9" t="s">
@@ -43085,16 +43087,16 @@
         <v>4</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="H9" s="11" t="s">
         <v>9</v>
@@ -43106,32 +43108,32 @@
         <v>301</v>
       </c>
       <c r="K9" s="14" t="s">
-        <v>902</v>
-      </c>
-      <c r="L9" s="141" t="s">
-        <v>1103</v>
-      </c>
-      <c r="M9" s="142" t="s">
+        <v>903</v>
+      </c>
+      <c r="L9" s="140" t="s">
         <v>1104</v>
       </c>
-      <c r="N9" s="142" t="s">
+      <c r="M9" s="141" t="s">
         <v>1105</v>
       </c>
-      <c r="O9" s="143" t="s">
+      <c r="N9" s="141" t="s">
         <v>1106</v>
+      </c>
+      <c r="O9" s="142" t="s">
+        <v>1107</v>
       </c>
     </row>
     <row r="10" ht="58.5" customHeight="1">
       <c r="A10" s="16" t="s">
-        <v>1107</v>
-      </c>
-      <c r="B10" s="157" t="s">
         <v>1108</v>
       </c>
-      <c r="C10" s="147">
+      <c r="B10" s="156" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C10" s="146">
         <v>0.0</v>
       </c>
-      <c r="D10" s="148">
+      <c r="D10" s="147">
         <v>15.0</v>
       </c>
       <c r="E10" s="61">
@@ -43139,39 +43141,39 @@
       </c>
       <c r="F10" s="11"/>
       <c r="G10" s="11"/>
-      <c r="H10" s="158">
+      <c r="H10" s="157">
         <f>SUM(D10:G10)</f>
         <v>25</v>
       </c>
-      <c r="I10" s="146">
+      <c r="I10" s="145">
         <v>30.0</v>
       </c>
-      <c r="J10" s="159">
+      <c r="J10" s="158">
         <v>0.15</v>
       </c>
-      <c r="K10" s="146" t="s">
-        <v>1109</v>
-      </c>
-      <c r="L10" s="146" t="s">
+      <c r="K10" s="145" t="s">
         <v>1110</v>
       </c>
+      <c r="L10" s="145" t="s">
+        <v>1111</v>
+      </c>
       <c r="M10" s="49" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="N10" s="11"/>
       <c r="O10" s="11"/>
     </row>
     <row r="11" ht="58.5" customHeight="1">
       <c r="A11" s="16" t="s">
-        <v>1112</v>
-      </c>
-      <c r="B11" s="157" t="s">
         <v>1113</v>
       </c>
-      <c r="C11" s="157" t="s">
+      <c r="B11" s="156" t="s">
         <v>1114</v>
       </c>
-      <c r="D11" s="148">
+      <c r="C11" s="156" t="s">
+        <v>1115</v>
+      </c>
+      <c r="D11" s="147">
         <v>5.0</v>
       </c>
       <c r="E11" s="61">
@@ -43179,38 +43181,38 @@
       </c>
       <c r="F11" s="11"/>
       <c r="G11" s="11"/>
-      <c r="H11" s="146">
+      <c r="H11" s="145">
         <v>5.0</v>
       </c>
-      <c r="I11" s="146">
+      <c r="I11" s="145">
         <v>5.0</v>
       </c>
-      <c r="J11" s="149">
+      <c r="J11" s="148">
         <v>0.72</v>
       </c>
-      <c r="K11" s="147" t="s">
-        <v>1115</v>
-      </c>
-      <c r="L11" s="146" t="s">
+      <c r="K11" s="146" t="s">
         <v>1116</v>
       </c>
-      <c r="M11" s="146" t="s">
+      <c r="L11" s="145" t="s">
         <v>1117</v>
+      </c>
+      <c r="M11" s="145" t="s">
+        <v>1118</v>
       </c>
       <c r="N11" s="11"/>
       <c r="O11" s="11"/>
     </row>
     <row r="12" ht="58.5" customHeight="1">
       <c r="A12" s="16" t="s">
-        <v>1118</v>
-      </c>
-      <c r="B12" s="157" t="s">
         <v>1119</v>
       </c>
-      <c r="C12" s="147">
+      <c r="B12" s="156" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C12" s="146">
         <v>0.0</v>
       </c>
-      <c r="D12" s="147">
+      <c r="D12" s="146">
         <v>450.0</v>
       </c>
       <c r="E12" s="61">
@@ -43218,40 +43220,40 @@
       </c>
       <c r="F12" s="11"/>
       <c r="G12" s="11"/>
-      <c r="H12" s="146">
+      <c r="H12" s="145">
         <f t="shared" ref="H12:H19" si="1">SUM(D12:G12)</f>
         <v>3550</v>
       </c>
-      <c r="I12" s="146">
+      <c r="I12" s="145">
         <v>3300.0</v>
       </c>
-      <c r="J12" s="160">
+      <c r="J12" s="159">
         <f t="shared" ref="J12:J19" si="2">H12/I12</f>
         <v>1.075757576</v>
       </c>
-      <c r="K12" s="146" t="s">
-        <v>1120</v>
-      </c>
-      <c r="L12" s="146" t="s">
+      <c r="K12" s="145" t="s">
         <v>1121</v>
       </c>
-      <c r="M12" s="146" t="s">
+      <c r="L12" s="145" t="s">
         <v>1122</v>
+      </c>
+      <c r="M12" s="145" t="s">
+        <v>1123</v>
       </c>
       <c r="N12" s="11"/>
       <c r="O12" s="11"/>
     </row>
     <row r="13" ht="58.5" customHeight="1">
       <c r="A13" s="16" t="s">
-        <v>1123</v>
-      </c>
-      <c r="B13" s="157" t="s">
         <v>1124</v>
       </c>
-      <c r="C13" s="161" t="s">
+      <c r="B13" s="156" t="s">
         <v>1125</v>
       </c>
-      <c r="D13" s="147">
+      <c r="C13" s="160" t="s">
+        <v>1126</v>
+      </c>
+      <c r="D13" s="146">
         <v>3.39</v>
       </c>
       <c r="E13" s="61">
@@ -43259,81 +43261,81 @@
       </c>
       <c r="F13" s="11"/>
       <c r="G13" s="11"/>
-      <c r="H13" s="146">
+      <c r="H13" s="145">
         <f t="shared" si="1"/>
         <v>3.39</v>
       </c>
-      <c r="I13" s="146">
+      <c r="I13" s="145">
         <v>20.0</v>
       </c>
-      <c r="J13" s="159">
+      <c r="J13" s="158">
         <f t="shared" si="2"/>
         <v>0.1695</v>
       </c>
-      <c r="K13" s="157" t="s">
-        <v>1126</v>
-      </c>
-      <c r="L13" s="146" t="s">
+      <c r="K13" s="156" t="s">
         <v>1127</v>
       </c>
-      <c r="M13" s="146" t="s">
+      <c r="L13" s="145" t="s">
         <v>1128</v>
+      </c>
+      <c r="M13" s="145" t="s">
+        <v>1129</v>
       </c>
       <c r="N13" s="11"/>
       <c r="O13" s="11"/>
     </row>
     <row r="14" ht="58.5" customHeight="1">
       <c r="A14" s="32" t="s">
-        <v>1129</v>
-      </c>
-      <c r="B14" s="157" t="s">
         <v>1130</v>
       </c>
-      <c r="C14" s="157" t="s">
+      <c r="B14" s="156" t="s">
         <v>1131</v>
       </c>
-      <c r="D14" s="147">
+      <c r="C14" s="156" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D14" s="146">
         <v>0.0</v>
       </c>
       <c r="E14" s="61" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="F14" s="11"/>
       <c r="G14" s="11"/>
-      <c r="H14" s="146">
+      <c r="H14" s="145">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I14" s="146">
+      <c r="I14" s="145">
         <v>5.0</v>
       </c>
-      <c r="J14" s="159">
+      <c r="J14" s="158">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K14" s="146" t="s">
+      <c r="K14" s="145" t="s">
+        <v>1134</v>
+      </c>
+      <c r="L14" s="145" t="s">
         <v>1133</v>
       </c>
-      <c r="L14" s="146" t="s">
-        <v>1132</v>
-      </c>
-      <c r="M14" s="146" t="s">
-        <v>1134</v>
+      <c r="M14" s="145" t="s">
+        <v>1135</v>
       </c>
       <c r="N14" s="11"/>
       <c r="O14" s="11"/>
     </row>
     <row r="15" ht="58.5" customHeight="1">
       <c r="A15" s="32" t="s">
-        <v>1129</v>
-      </c>
-      <c r="B15" s="157" t="s">
-        <v>1135</v>
-      </c>
-      <c r="C15" s="157" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B15" s="156" t="s">
         <v>1136</v>
       </c>
-      <c r="D15" s="147">
+      <c r="C15" s="156" t="s">
+        <v>1137</v>
+      </c>
+      <c r="D15" s="146">
         <v>47.0</v>
       </c>
       <c r="E15" s="61">
@@ -43341,40 +43343,40 @@
       </c>
       <c r="F15" s="11"/>
       <c r="G15" s="11"/>
-      <c r="H15" s="146">
+      <c r="H15" s="145">
         <f t="shared" si="1"/>
         <v>112</v>
       </c>
-      <c r="I15" s="146">
+      <c r="I15" s="145">
         <v>80.0</v>
       </c>
-      <c r="J15" s="160">
+      <c r="J15" s="159">
         <f t="shared" si="2"/>
         <v>1.4</v>
       </c>
-      <c r="K15" s="146" t="s">
-        <v>1137</v>
-      </c>
-      <c r="L15" s="146" t="s">
+      <c r="K15" s="145" t="s">
         <v>1138</v>
       </c>
-      <c r="M15" s="146" t="s">
+      <c r="L15" s="145" t="s">
         <v>1139</v>
+      </c>
+      <c r="M15" s="145" t="s">
+        <v>1140</v>
       </c>
       <c r="N15" s="11"/>
       <c r="O15" s="11"/>
     </row>
     <row r="16" ht="58.5" customHeight="1">
       <c r="A16" s="20" t="s">
-        <v>1140</v>
-      </c>
-      <c r="B16" s="157" t="s">
         <v>1141</v>
       </c>
-      <c r="C16" s="157" t="s">
+      <c r="B16" s="156" t="s">
         <v>1142</v>
       </c>
-      <c r="D16" s="147">
+      <c r="C16" s="156" t="s">
+        <v>1143</v>
+      </c>
+      <c r="D16" s="146">
         <v>0.0</v>
       </c>
       <c r="E16" s="61">
@@ -43382,40 +43384,40 @@
       </c>
       <c r="F16" s="11"/>
       <c r="G16" s="11"/>
-      <c r="H16" s="146">
+      <c r="H16" s="145">
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
-      <c r="I16" s="146">
+      <c r="I16" s="145">
         <v>21.0</v>
       </c>
-      <c r="J16" s="160">
+      <c r="J16" s="159">
         <f t="shared" si="2"/>
         <v>2.857142857</v>
       </c>
-      <c r="K16" s="146" t="s">
-        <v>1143</v>
-      </c>
-      <c r="L16" s="146" t="s">
-        <v>1132</v>
-      </c>
-      <c r="M16" s="146" t="s">
+      <c r="K16" s="145" t="s">
         <v>1144</v>
+      </c>
+      <c r="L16" s="145" t="s">
+        <v>1133</v>
+      </c>
+      <c r="M16" s="145" t="s">
+        <v>1145</v>
       </c>
       <c r="N16" s="11"/>
       <c r="O16" s="11"/>
     </row>
     <row r="17" ht="58.5" customHeight="1">
       <c r="A17" s="33" t="s">
-        <v>1145</v>
-      </c>
-      <c r="B17" s="157" t="s">
         <v>1146</v>
       </c>
-      <c r="C17" s="162" t="s">
+      <c r="B17" s="156" t="s">
         <v>1147</v>
       </c>
-      <c r="D17" s="147">
+      <c r="C17" s="161" t="s">
+        <v>1148</v>
+      </c>
+      <c r="D17" s="146">
         <v>0.0</v>
       </c>
       <c r="E17" s="61">
@@ -43423,40 +43425,40 @@
       </c>
       <c r="F17" s="11"/>
       <c r="G17" s="11"/>
-      <c r="H17" s="146">
+      <c r="H17" s="145">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="I17" s="146">
+      <c r="I17" s="145">
         <v>7.0</v>
       </c>
-      <c r="J17" s="160">
+      <c r="J17" s="159">
         <f t="shared" si="2"/>
         <v>1.428571429</v>
       </c>
-      <c r="K17" s="146" t="s">
-        <v>1148</v>
-      </c>
-      <c r="L17" s="146" t="s">
-        <v>1132</v>
-      </c>
-      <c r="M17" s="146" t="s">
+      <c r="K17" s="145" t="s">
         <v>1149</v>
+      </c>
+      <c r="L17" s="145" t="s">
+        <v>1133</v>
+      </c>
+      <c r="M17" s="145" t="s">
+        <v>1150</v>
       </c>
       <c r="N17" s="11"/>
       <c r="O17" s="11"/>
     </row>
     <row r="18" ht="58.5" customHeight="1">
       <c r="A18" s="33" t="s">
-        <v>1145</v>
-      </c>
-      <c r="B18" s="157" t="s">
-        <v>1150</v>
-      </c>
-      <c r="C18" s="162" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B18" s="156" t="s">
         <v>1151</v>
       </c>
-      <c r="D18" s="147">
+      <c r="C18" s="161" t="s">
+        <v>1152</v>
+      </c>
+      <c r="D18" s="146">
         <v>0.0</v>
       </c>
       <c r="E18" s="61">
@@ -43464,40 +43466,40 @@
       </c>
       <c r="F18" s="11"/>
       <c r="G18" s="11"/>
-      <c r="H18" s="146">
+      <c r="H18" s="145">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I18" s="146">
+      <c r="I18" s="145">
         <v>1.0</v>
       </c>
-      <c r="J18" s="159">
+      <c r="J18" s="158">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K18" s="146" t="s">
-        <v>1152</v>
-      </c>
-      <c r="L18" s="146" t="s">
-        <v>1132</v>
-      </c>
-      <c r="M18" s="163" t="s">
+      <c r="K18" s="145" t="s">
         <v>1153</v>
+      </c>
+      <c r="L18" s="145" t="s">
+        <v>1133</v>
+      </c>
+      <c r="M18" s="162" t="s">
+        <v>1154</v>
       </c>
       <c r="N18" s="11"/>
       <c r="O18" s="11"/>
     </row>
     <row r="19" ht="58.5" customHeight="1">
       <c r="A19" s="33" t="s">
-        <v>1145</v>
-      </c>
-      <c r="B19" s="161" t="s">
-        <v>1154</v>
-      </c>
-      <c r="C19" s="162" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B19" s="160" t="s">
         <v>1155</v>
       </c>
-      <c r="D19" s="147">
+      <c r="C19" s="161" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D19" s="146">
         <v>0.0</v>
       </c>
       <c r="E19" s="61">
@@ -43505,181 +43507,181 @@
       </c>
       <c r="F19" s="11"/>
       <c r="G19" s="11"/>
-      <c r="H19" s="146">
+      <c r="H19" s="145">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I19" s="146">
+      <c r="I19" s="145">
         <v>4.0</v>
       </c>
-      <c r="J19" s="159">
+      <c r="J19" s="158">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K19" s="146" t="s">
-        <v>1156</v>
-      </c>
-      <c r="L19" s="146" t="s">
-        <v>1132</v>
-      </c>
-      <c r="M19" s="146" t="s">
+      <c r="K19" s="145" t="s">
         <v>1157</v>
+      </c>
+      <c r="L19" s="145" t="s">
+        <v>1133</v>
+      </c>
+      <c r="M19" s="145" t="s">
+        <v>1158</v>
       </c>
       <c r="N19" s="11"/>
       <c r="O19" s="11"/>
     </row>
     <row r="20" ht="14.25" customHeight="1">
-      <c r="A20" s="126"/>
-      <c r="B20" s="126"/>
-      <c r="C20" s="126"/>
-      <c r="D20" s="126"/>
-      <c r="E20" s="126"/>
-      <c r="F20" s="126"/>
-      <c r="G20" s="126"/>
-      <c r="H20" s="126"/>
-      <c r="I20" s="126"/>
-      <c r="J20" s="126"/>
-      <c r="K20" s="126"/>
-      <c r="L20" s="126"/>
-      <c r="M20" s="126"/>
-      <c r="N20" s="126"/>
-      <c r="O20" s="126"/>
+      <c r="A20" s="125"/>
+      <c r="B20" s="125"/>
+      <c r="C20" s="125"/>
+      <c r="D20" s="125"/>
+      <c r="E20" s="125"/>
+      <c r="F20" s="125"/>
+      <c r="G20" s="125"/>
+      <c r="H20" s="125"/>
+      <c r="I20" s="125"/>
+      <c r="J20" s="125"/>
+      <c r="K20" s="125"/>
+      <c r="L20" s="125"/>
+      <c r="M20" s="125"/>
+      <c r="N20" s="125"/>
+      <c r="O20" s="125"/>
     </row>
     <row r="21" ht="14.25" customHeight="1">
-      <c r="A21" s="126"/>
-      <c r="B21" s="126"/>
-      <c r="C21" s="126"/>
-      <c r="D21" s="126"/>
-      <c r="E21" s="126"/>
-      <c r="F21" s="126"/>
-      <c r="G21" s="126"/>
-      <c r="H21" s="126"/>
-      <c r="I21" s="126"/>
-      <c r="J21" s="126"/>
-      <c r="K21" s="126"/>
-      <c r="L21" s="126"/>
-      <c r="M21" s="126"/>
-      <c r="N21" s="126"/>
-      <c r="O21" s="126"/>
+      <c r="A21" s="125"/>
+      <c r="B21" s="125"/>
+      <c r="C21" s="125"/>
+      <c r="D21" s="125"/>
+      <c r="E21" s="125"/>
+      <c r="F21" s="125"/>
+      <c r="G21" s="125"/>
+      <c r="H21" s="125"/>
+      <c r="I21" s="125"/>
+      <c r="J21" s="125"/>
+      <c r="K21" s="125"/>
+      <c r="L21" s="125"/>
+      <c r="M21" s="125"/>
+      <c r="N21" s="125"/>
+      <c r="O21" s="125"/>
     </row>
     <row r="22" ht="14.25" customHeight="1">
-      <c r="A22" s="126"/>
-      <c r="B22" s="126"/>
-      <c r="C22" s="126"/>
-      <c r="D22" s="126"/>
-      <c r="E22" s="126"/>
-      <c r="F22" s="126"/>
-      <c r="G22" s="126"/>
-      <c r="H22" s="126"/>
-      <c r="I22" s="126"/>
-      <c r="J22" s="126"/>
-      <c r="K22" s="126"/>
-      <c r="L22" s="126"/>
-      <c r="M22" s="126"/>
-      <c r="N22" s="126"/>
-      <c r="O22" s="126"/>
+      <c r="A22" s="125"/>
+      <c r="B22" s="125"/>
+      <c r="C22" s="125"/>
+      <c r="D22" s="125"/>
+      <c r="E22" s="125"/>
+      <c r="F22" s="125"/>
+      <c r="G22" s="125"/>
+      <c r="H22" s="125"/>
+      <c r="I22" s="125"/>
+      <c r="J22" s="125"/>
+      <c r="K22" s="125"/>
+      <c r="L22" s="125"/>
+      <c r="M22" s="125"/>
+      <c r="N22" s="125"/>
+      <c r="O22" s="125"/>
     </row>
     <row r="23" ht="14.25" customHeight="1">
-      <c r="A23" s="126"/>
-      <c r="B23" s="126"/>
-      <c r="C23" s="126"/>
-      <c r="D23" s="126"/>
-      <c r="E23" s="126"/>
-      <c r="F23" s="126"/>
-      <c r="G23" s="126"/>
-      <c r="H23" s="126"/>
-      <c r="I23" s="126"/>
-      <c r="J23" s="126"/>
-      <c r="K23" s="126"/>
-      <c r="L23" s="126"/>
-      <c r="M23" s="126"/>
-      <c r="N23" s="126"/>
-      <c r="O23" s="126"/>
+      <c r="A23" s="125"/>
+      <c r="B23" s="125"/>
+      <c r="C23" s="125"/>
+      <c r="D23" s="125"/>
+      <c r="E23" s="125"/>
+      <c r="F23" s="125"/>
+      <c r="G23" s="125"/>
+      <c r="H23" s="125"/>
+      <c r="I23" s="125"/>
+      <c r="J23" s="125"/>
+      <c r="K23" s="125"/>
+      <c r="L23" s="125"/>
+      <c r="M23" s="125"/>
+      <c r="N23" s="125"/>
+      <c r="O23" s="125"/>
     </row>
     <row r="24" ht="14.25" customHeight="1">
-      <c r="A24" s="126"/>
-      <c r="B24" s="126"/>
-      <c r="C24" s="126"/>
-      <c r="D24" s="126"/>
-      <c r="E24" s="126"/>
-      <c r="F24" s="126"/>
-      <c r="G24" s="126"/>
-      <c r="H24" s="126"/>
-      <c r="I24" s="126"/>
-      <c r="J24" s="126"/>
-      <c r="K24" s="126"/>
-      <c r="L24" s="126"/>
-      <c r="M24" s="126"/>
-      <c r="N24" s="126"/>
-      <c r="O24" s="126"/>
+      <c r="A24" s="125"/>
+      <c r="B24" s="125"/>
+      <c r="C24" s="125"/>
+      <c r="D24" s="125"/>
+      <c r="E24" s="125"/>
+      <c r="F24" s="125"/>
+      <c r="G24" s="125"/>
+      <c r="H24" s="125"/>
+      <c r="I24" s="125"/>
+      <c r="J24" s="125"/>
+      <c r="K24" s="125"/>
+      <c r="L24" s="125"/>
+      <c r="M24" s="125"/>
+      <c r="N24" s="125"/>
+      <c r="O24" s="125"/>
     </row>
     <row r="25" ht="14.25" customHeight="1">
-      <c r="A25" s="126"/>
-      <c r="B25" s="126"/>
-      <c r="C25" s="126"/>
-      <c r="D25" s="126"/>
-      <c r="E25" s="126"/>
-      <c r="F25" s="126"/>
-      <c r="G25" s="126"/>
-      <c r="H25" s="126"/>
-      <c r="I25" s="126"/>
-      <c r="J25" s="126"/>
-      <c r="K25" s="126"/>
-      <c r="L25" s="126"/>
-      <c r="M25" s="126"/>
-      <c r="N25" s="126"/>
-      <c r="O25" s="126"/>
+      <c r="A25" s="125"/>
+      <c r="B25" s="125"/>
+      <c r="C25" s="125"/>
+      <c r="D25" s="125"/>
+      <c r="E25" s="125"/>
+      <c r="F25" s="125"/>
+      <c r="G25" s="125"/>
+      <c r="H25" s="125"/>
+      <c r="I25" s="125"/>
+      <c r="J25" s="125"/>
+      <c r="K25" s="125"/>
+      <c r="L25" s="125"/>
+      <c r="M25" s="125"/>
+      <c r="N25" s="125"/>
+      <c r="O25" s="125"/>
     </row>
     <row r="26" ht="14.25" customHeight="1">
-      <c r="A26" s="126"/>
-      <c r="B26" s="126"/>
-      <c r="C26" s="126"/>
-      <c r="D26" s="126"/>
-      <c r="E26" s="126"/>
-      <c r="F26" s="126"/>
-      <c r="G26" s="126"/>
-      <c r="H26" s="126"/>
-      <c r="I26" s="126"/>
-      <c r="J26" s="126"/>
-      <c r="K26" s="126"/>
-      <c r="L26" s="126"/>
-      <c r="M26" s="126"/>
-      <c r="N26" s="126"/>
-      <c r="O26" s="126"/>
+      <c r="A26" s="125"/>
+      <c r="B26" s="125"/>
+      <c r="C26" s="125"/>
+      <c r="D26" s="125"/>
+      <c r="E26" s="125"/>
+      <c r="F26" s="125"/>
+      <c r="G26" s="125"/>
+      <c r="H26" s="125"/>
+      <c r="I26" s="125"/>
+      <c r="J26" s="125"/>
+      <c r="K26" s="125"/>
+      <c r="L26" s="125"/>
+      <c r="M26" s="125"/>
+      <c r="N26" s="125"/>
+      <c r="O26" s="125"/>
     </row>
     <row r="27" ht="14.25" customHeight="1">
-      <c r="A27" s="126"/>
-      <c r="B27" s="126"/>
-      <c r="C27" s="126"/>
-      <c r="D27" s="126"/>
-      <c r="E27" s="126"/>
-      <c r="F27" s="126"/>
-      <c r="G27" s="126"/>
-      <c r="H27" s="126"/>
-      <c r="I27" s="126"/>
-      <c r="J27" s="126"/>
-      <c r="K27" s="126"/>
-      <c r="L27" s="126"/>
-      <c r="M27" s="126"/>
-      <c r="N27" s="126"/>
-      <c r="O27" s="126"/>
+      <c r="A27" s="125"/>
+      <c r="B27" s="125"/>
+      <c r="C27" s="125"/>
+      <c r="D27" s="125"/>
+      <c r="E27" s="125"/>
+      <c r="F27" s="125"/>
+      <c r="G27" s="125"/>
+      <c r="H27" s="125"/>
+      <c r="I27" s="125"/>
+      <c r="J27" s="125"/>
+      <c r="K27" s="125"/>
+      <c r="L27" s="125"/>
+      <c r="M27" s="125"/>
+      <c r="N27" s="125"/>
+      <c r="O27" s="125"/>
     </row>
     <row r="28" ht="14.25" customHeight="1">
-      <c r="A28" s="126"/>
-      <c r="B28" s="126"/>
-      <c r="C28" s="126"/>
-      <c r="D28" s="126"/>
-      <c r="E28" s="126"/>
-      <c r="F28" s="126"/>
-      <c r="G28" s="126"/>
-      <c r="H28" s="126"/>
-      <c r="I28" s="126"/>
-      <c r="J28" s="126"/>
-      <c r="K28" s="126"/>
-      <c r="L28" s="126"/>
-      <c r="M28" s="126"/>
-      <c r="N28" s="126"/>
-      <c r="O28" s="126"/>
+      <c r="A28" s="125"/>
+      <c r="B28" s="125"/>
+      <c r="C28" s="125"/>
+      <c r="D28" s="125"/>
+      <c r="E28" s="125"/>
+      <c r="F28" s="125"/>
+      <c r="G28" s="125"/>
+      <c r="H28" s="125"/>
+      <c r="I28" s="125"/>
+      <c r="J28" s="125"/>
+      <c r="K28" s="125"/>
+      <c r="L28" s="125"/>
+      <c r="M28" s="125"/>
+      <c r="N28" s="125"/>
+      <c r="O28" s="125"/>
     </row>
     <row r="29" ht="14.25" customHeight="1"/>
     <row r="30" ht="14.25" customHeight="1"/>
@@ -56532,25 +56534,29 @@
       <c r="A6" s="38" t="s">
         <v>569</v>
       </c>
-      <c r="B6" s="87"/>
-      <c r="C6" s="87"/>
-      <c r="D6" s="88">
+      <c r="B6" s="38" t="s">
+        <v>575</v>
+      </c>
+      <c r="C6" s="38" t="s">
+        <v>571</v>
+      </c>
+      <c r="D6" s="87">
         <v>1.0</v>
       </c>
-      <c r="E6" s="88">
+      <c r="E6" s="87">
         <v>0.0</v>
       </c>
-      <c r="F6" s="89">
+      <c r="F6" s="88">
         <v>0.0</v>
       </c>
-      <c r="G6" s="89">
+      <c r="G6" s="88">
         <v>0.0</v>
       </c>
       <c r="H6" s="84">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="I6" s="89">
+      <c r="I6" s="88">
         <v>2.0</v>
       </c>
       <c r="J6" s="34">
@@ -56558,44 +56564,44 @@
         <v>0.5</v>
       </c>
       <c r="K6" s="18" t="s">
-        <v>575</v>
-      </c>
-      <c r="L6" s="90" t="s">
         <v>576</v>
       </c>
-      <c r="M6" s="91" t="s">
+      <c r="L6" s="89" t="s">
         <v>577</v>
       </c>
-      <c r="N6" s="92"/>
-      <c r="O6" s="92"/>
+      <c r="M6" s="90" t="s">
+        <v>578</v>
+      </c>
+      <c r="N6" s="91"/>
+      <c r="O6" s="91"/>
     </row>
     <row r="7" ht="33.75" customHeight="1">
       <c r="A7" s="32" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>580</v>
-      </c>
-      <c r="D7" s="93">
+        <v>581</v>
+      </c>
+      <c r="D7" s="92">
         <v>5.0</v>
       </c>
-      <c r="E7" s="94">
+      <c r="E7" s="93">
         <v>0.0</v>
       </c>
-      <c r="F7" s="94">
+      <c r="F7" s="93">
         <v>0.0</v>
       </c>
-      <c r="G7" s="94">
+      <c r="G7" s="93">
         <v>0.0</v>
       </c>
       <c r="H7" s="84">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="I7" s="94">
+      <c r="I7" s="93">
         <v>5.0</v>
       </c>
       <c r="J7" s="34">
@@ -56603,26 +56609,26 @@
         <v>1</v>
       </c>
       <c r="K7" s="18" t="s">
-        <v>581</v>
-      </c>
-      <c r="L7" s="95" t="s">
         <v>582</v>
       </c>
-      <c r="M7" s="95" t="s">
+      <c r="L7" s="94" t="s">
         <v>583</v>
       </c>
-      <c r="N7" s="96"/>
-      <c r="O7" s="96"/>
+      <c r="M7" s="94" t="s">
+        <v>584</v>
+      </c>
+      <c r="N7" s="95"/>
+      <c r="O7" s="95"/>
     </row>
     <row r="8" ht="33.75" customHeight="1">
       <c r="A8" s="32" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D8" s="83">
         <v>2.0</v>
@@ -56648,42 +56654,42 @@
         <v>1</v>
       </c>
       <c r="K8" s="18" t="s">
-        <v>586</v>
-      </c>
-      <c r="L8" s="97" t="s">
         <v>587</v>
       </c>
-      <c r="M8" s="97" t="s">
+      <c r="L8" s="96" t="s">
         <v>588</v>
+      </c>
+      <c r="M8" s="96" t="s">
+        <v>589</v>
       </c>
       <c r="N8" s="86"/>
       <c r="O8" s="86"/>
     </row>
     <row r="9" ht="33.75" customHeight="1">
       <c r="A9" s="32" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C9" s="17"/>
-      <c r="D9" s="88">
+      <c r="D9" s="87">
         <v>59.0</v>
       </c>
-      <c r="E9" s="89">
+      <c r="E9" s="88">
         <v>0.0</v>
       </c>
-      <c r="F9" s="89">
+      <c r="F9" s="88">
         <v>0.0</v>
       </c>
-      <c r="G9" s="89">
+      <c r="G9" s="88">
         <v>0.0</v>
       </c>
       <c r="H9" s="84">
         <f t="shared" si="1"/>
         <v>59</v>
       </c>
-      <c r="I9" s="89">
+      <c r="I9" s="88">
         <v>50.0</v>
       </c>
       <c r="J9" s="34">
@@ -56691,44 +56697,44 @@
         <v>1.18</v>
       </c>
       <c r="K9" s="18" t="s">
-        <v>590</v>
-      </c>
-      <c r="L9" s="91" t="s">
         <v>591</v>
       </c>
-      <c r="M9" s="91" t="s">
+      <c r="L9" s="90" t="s">
         <v>592</v>
       </c>
-      <c r="N9" s="92"/>
-      <c r="O9" s="92"/>
+      <c r="M9" s="90" t="s">
+        <v>593</v>
+      </c>
+      <c r="N9" s="91"/>
+      <c r="O9" s="91"/>
     </row>
     <row r="10" ht="33.75" customHeight="1">
       <c r="A10" s="17" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>595</v>
-      </c>
-      <c r="D10" s="93">
+        <v>596</v>
+      </c>
+      <c r="D10" s="92">
         <v>1.0</v>
       </c>
-      <c r="E10" s="93">
+      <c r="E10" s="92">
         <v>3.0</v>
       </c>
-      <c r="F10" s="94">
+      <c r="F10" s="93">
         <v>0.0</v>
       </c>
-      <c r="G10" s="94">
+      <c r="G10" s="93">
         <v>0.0</v>
       </c>
       <c r="H10" s="84">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="I10" s="93">
+      <c r="I10" s="92">
         <v>5.0</v>
       </c>
       <c r="J10" s="34">
@@ -56736,26 +56742,26 @@
         <v>0.8</v>
       </c>
       <c r="K10" s="18" t="s">
-        <v>596</v>
-      </c>
-      <c r="L10" s="95" t="s">
         <v>597</v>
       </c>
-      <c r="M10" s="95" t="s">
+      <c r="L10" s="94" t="s">
         <v>598</v>
       </c>
-      <c r="N10" s="96"/>
-      <c r="O10" s="96"/>
+      <c r="M10" s="94" t="s">
+        <v>599</v>
+      </c>
+      <c r="N10" s="95"/>
+      <c r="O10" s="95"/>
     </row>
     <row r="11" ht="33.75" customHeight="1">
       <c r="A11" s="17" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D11" s="83">
         <v>54.0</v>
@@ -56781,50 +56787,50 @@
         <v>1.08</v>
       </c>
       <c r="K11" s="18" t="s">
-        <v>602</v>
-      </c>
-      <c r="L11" s="97" t="s">
         <v>603</v>
       </c>
-      <c r="M11" s="97" t="s">
+      <c r="L11" s="96" t="s">
         <v>604</v>
+      </c>
+      <c r="M11" s="96" t="s">
+        <v>605</v>
       </c>
       <c r="N11" s="86"/>
       <c r="O11" s="86"/>
     </row>
     <row r="12" ht="33.75" customHeight="1">
-      <c r="A12" s="98"/>
-      <c r="B12" s="98"/>
-      <c r="C12" s="98"/>
-      <c r="D12" s="98"/>
-      <c r="E12" s="98"/>
-      <c r="F12" s="98"/>
-      <c r="G12" s="98"/>
-      <c r="H12" s="98"/>
-      <c r="I12" s="98"/>
-      <c r="J12" s="98"/>
-      <c r="K12" s="98"/>
-      <c r="L12" s="98"/>
-      <c r="M12" s="98"/>
-      <c r="N12" s="98"/>
-      <c r="O12" s="98"/>
+      <c r="A12" s="97"/>
+      <c r="B12" s="97"/>
+      <c r="C12" s="97"/>
+      <c r="D12" s="97"/>
+      <c r="E12" s="97"/>
+      <c r="F12" s="97"/>
+      <c r="G12" s="97"/>
+      <c r="H12" s="97"/>
+      <c r="I12" s="97"/>
+      <c r="J12" s="97"/>
+      <c r="K12" s="97"/>
+      <c r="L12" s="97"/>
+      <c r="M12" s="97"/>
+      <c r="N12" s="97"/>
+      <c r="O12" s="97"/>
     </row>
     <row r="13" ht="33.75" customHeight="1">
-      <c r="A13" s="99"/>
-      <c r="B13" s="99"/>
-      <c r="C13" s="99"/>
-      <c r="D13" s="99"/>
-      <c r="E13" s="99"/>
-      <c r="F13" s="99"/>
-      <c r="G13" s="99"/>
-      <c r="H13" s="99"/>
-      <c r="I13" s="99"/>
-      <c r="J13" s="99"/>
-      <c r="K13" s="99"/>
-      <c r="L13" s="99"/>
-      <c r="M13" s="99"/>
-      <c r="N13" s="99"/>
-      <c r="O13" s="99"/>
+      <c r="A13" s="98"/>
+      <c r="B13" s="98"/>
+      <c r="C13" s="98"/>
+      <c r="D13" s="98"/>
+      <c r="E13" s="98"/>
+      <c r="F13" s="98"/>
+      <c r="G13" s="98"/>
+      <c r="H13" s="98"/>
+      <c r="I13" s="98"/>
+      <c r="J13" s="98"/>
+      <c r="K13" s="98"/>
+      <c r="L13" s="98"/>
+      <c r="M13" s="98"/>
+      <c r="N13" s="98"/>
+      <c r="O13" s="98"/>
     </row>
     <row r="14" ht="33.75" customHeight="1">
       <c r="A14" s="78" t="s">
@@ -56856,16 +56862,16 @@
         <v>4</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H15" s="11" t="s">
         <v>9</v>
@@ -56880,27 +56886,27 @@
         <v>12</v>
       </c>
       <c r="L15" s="11" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="M15" s="11" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="N15" s="11" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="O15" s="11" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="16" ht="33.75" customHeight="1">
       <c r="A16" s="17" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D16" s="18">
         <v>0.0</v>
@@ -56926,26 +56932,26 @@
         <v>1</v>
       </c>
       <c r="K16" s="18" t="s">
-        <v>616</v>
-      </c>
-      <c r="L16" s="97" t="s">
         <v>617</v>
       </c>
-      <c r="M16" s="97" t="s">
+      <c r="L16" s="96" t="s">
         <v>618</v>
+      </c>
+      <c r="M16" s="96" t="s">
+        <v>619</v>
       </c>
       <c r="N16" s="86"/>
       <c r="O16" s="86"/>
     </row>
     <row r="17" ht="33.75" customHeight="1">
       <c r="A17" s="38" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="D17" s="18">
         <v>0.0</v>
@@ -56971,23 +56977,23 @@
         <v>1.2</v>
       </c>
       <c r="K17" s="17" t="s">
-        <v>622</v>
-      </c>
-      <c r="L17" s="100" t="s">
         <v>623</v>
       </c>
+      <c r="L17" s="99" t="s">
+        <v>624</v>
+      </c>
       <c r="M17" s="57" t="s">
-        <v>624</v>
-      </c>
-      <c r="N17" s="101"/>
-      <c r="O17" s="102"/>
+        <v>625</v>
+      </c>
+      <c r="N17" s="100"/>
+      <c r="O17" s="101"/>
     </row>
     <row r="18" ht="33.75" customHeight="1">
       <c r="A18" s="38" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C18" s="17"/>
       <c r="D18" s="17">
@@ -57014,26 +57020,26 @@
         <v>0</v>
       </c>
       <c r="K18" s="17" t="s">
-        <v>627</v>
-      </c>
-      <c r="L18" s="103" t="s">
         <v>628</v>
       </c>
+      <c r="L18" s="102" t="s">
+        <v>629</v>
+      </c>
       <c r="M18" s="57" t="s">
-        <v>629</v>
-      </c>
-      <c r="N18" s="101"/>
-      <c r="O18" s="102"/>
+        <v>630</v>
+      </c>
+      <c r="N18" s="100"/>
+      <c r="O18" s="101"/>
     </row>
     <row r="19" ht="33.75" customHeight="1">
       <c r="A19" s="17" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="D19" s="18">
         <v>36.0</v>
@@ -57059,26 +57065,26 @@
         <v>1.44</v>
       </c>
       <c r="K19" s="18" t="s">
-        <v>633</v>
-      </c>
-      <c r="L19" s="103" t="s">
         <v>634</v>
       </c>
+      <c r="L19" s="102" t="s">
+        <v>635</v>
+      </c>
       <c r="M19" s="57" t="s">
-        <v>635</v>
-      </c>
-      <c r="N19" s="101"/>
-      <c r="O19" s="102"/>
+        <v>636</v>
+      </c>
+      <c r="N19" s="100"/>
+      <c r="O19" s="101"/>
     </row>
     <row r="20" ht="33.75" customHeight="1">
       <c r="A20" s="38" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C20" s="38" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="D20" s="17">
         <v>0.0</v>
@@ -57104,26 +57110,26 @@
         <v>1</v>
       </c>
       <c r="K20" s="17" t="s">
-        <v>639</v>
-      </c>
-      <c r="L20" s="103" t="s">
         <v>640</v>
       </c>
+      <c r="L20" s="102" t="s">
+        <v>641</v>
+      </c>
       <c r="M20" s="57" t="s">
-        <v>641</v>
-      </c>
-      <c r="N20" s="101"/>
-      <c r="O20" s="102"/>
+        <v>642</v>
+      </c>
+      <c r="N20" s="100"/>
+      <c r="O20" s="101"/>
     </row>
     <row r="21" ht="33.75" customHeight="1">
       <c r="A21" s="38" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C21" s="38" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="D21" s="17">
         <v>0.0</v>
@@ -57149,26 +57155,26 @@
         <v>0</v>
       </c>
       <c r="K21" s="17" t="s">
-        <v>643</v>
-      </c>
-      <c r="L21" s="103" t="s">
         <v>644</v>
       </c>
-      <c r="M21" s="104" t="s">
+      <c r="L21" s="102" t="s">
         <v>645</v>
       </c>
-      <c r="N21" s="101"/>
-      <c r="O21" s="102"/>
+      <c r="M21" s="103" t="s">
+        <v>646</v>
+      </c>
+      <c r="N21" s="100"/>
+      <c r="O21" s="101"/>
     </row>
     <row r="22" ht="33.75" customHeight="1">
       <c r="A22" s="38" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B22" s="38" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C22" s="38" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="D22" s="18">
         <v>5.0</v>
@@ -57194,16 +57200,16 @@
         <v>1</v>
       </c>
       <c r="K22" s="17" t="s">
-        <v>647</v>
-      </c>
-      <c r="L22" s="103" t="s">
         <v>648</v>
       </c>
-      <c r="M22" s="103" t="s">
+      <c r="L22" s="102" t="s">
         <v>649</v>
       </c>
-      <c r="N22" s="102"/>
-      <c r="O22" s="102"/>
+      <c r="M22" s="102" t="s">
+        <v>650</v>
+      </c>
+      <c r="N22" s="101"/>
+      <c r="O22" s="101"/>
     </row>
     <row r="23" ht="14.25" customHeight="1"/>
     <row r="24" ht="14.25" customHeight="1"/>
@@ -58162,10 +58168,8 @@
     <row r="977" ht="14.25" customHeight="1"/>
     <row r="978" ht="14.25" customHeight="1"/>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="1">
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
@@ -58197,7 +58201,7 @@
   <sheetData>
     <row r="1" ht="32.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -58245,16 +58249,16 @@
         <v>4</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H4" s="11" t="s">
         <v>9</v>
@@ -58269,24 +58273,24 @@
         <v>12</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="5" ht="53.25" customHeight="1">
-      <c r="A5" s="105" t="s">
-        <v>659</v>
+      <c r="A5" s="104" t="s">
+        <v>660</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C5" s="17">
         <v>0.0</v>
@@ -58315,7 +58319,7 @@
         <v>1</v>
       </c>
       <c r="K5" s="17" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="L5" s="17"/>
       <c r="M5" s="17"/>
@@ -58323,11 +58327,11 @@
       <c r="O5" s="17"/>
     </row>
     <row r="6" ht="53.25" customHeight="1">
-      <c r="A6" s="105" t="s">
-        <v>659</v>
+      <c r="A6" s="104" t="s">
+        <v>660</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C6" s="17">
         <v>0.0</v>
@@ -58336,7 +58340,7 @@
         <f>2/12</f>
         <v>0.1666666667</v>
       </c>
-      <c r="E6" s="106">
+      <c r="E6" s="105">
         <v>0.3</v>
       </c>
       <c r="F6" s="17">
@@ -58357,21 +58361,21 @@
         <v>1.555555556</v>
       </c>
       <c r="K6" s="17" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="L6" s="17"/>
       <c r="M6" s="18" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="N6" s="17"/>
       <c r="O6" s="17"/>
     </row>
     <row r="7" ht="53.25" customHeight="1">
-      <c r="A7" s="105" t="s">
-        <v>659</v>
+      <c r="A7" s="104" t="s">
+        <v>660</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C7" s="17">
         <v>0.0</v>
@@ -58393,23 +58397,23 @@
         <v>0</v>
       </c>
       <c r="K7" s="17" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="L7" s="18" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="M7" s="18" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="N7" s="17"/>
       <c r="O7" s="17"/>
     </row>
     <row r="8" ht="53.25" customHeight="1">
-      <c r="A8" s="107" t="s">
-        <v>669</v>
+      <c r="A8" s="106" t="s">
+        <v>670</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C8" s="17">
         <v>0.0</v>
@@ -58438,23 +58442,23 @@
         <v>0</v>
       </c>
       <c r="K8" s="17" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="L8" s="18" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="M8" s="18" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="N8" s="17"/>
       <c r="O8" s="17"/>
     </row>
     <row r="9" ht="53.25" customHeight="1">
-      <c r="A9" s="107" t="s">
-        <v>669</v>
+      <c r="A9" s="106" t="s">
+        <v>670</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C9" s="17">
         <v>0.0</v>
@@ -58483,23 +58487,23 @@
         <v>0.3333333333</v>
       </c>
       <c r="K9" s="17" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="L9" s="18" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="M9" s="18" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="N9" s="17"/>
       <c r="O9" s="17"/>
     </row>
     <row r="10" ht="53.25" customHeight="1">
-      <c r="A10" s="107" t="s">
-        <v>669</v>
-      </c>
-      <c r="B10" s="108" t="s">
-        <v>677</v>
+      <c r="A10" s="106" t="s">
+        <v>670</v>
+      </c>
+      <c r="B10" s="107" t="s">
+        <v>678</v>
       </c>
       <c r="C10" s="17">
         <v>0.0</v>
@@ -58528,11 +58532,11 @@
         <v>0</v>
       </c>
       <c r="K10" s="18" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="L10" s="18"/>
       <c r="M10" s="18" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="N10" s="17"/>
       <c r="O10" s="17"/>
@@ -58568,16 +58572,16 @@
         <v>4</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H13" s="11" t="s">
         <v>9</v>
@@ -58592,24 +58596,24 @@
         <v>12</v>
       </c>
       <c r="L13" s="11" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="M13" s="11" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="N13" s="11" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="O13" s="11" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="14" ht="53.25" customHeight="1">
       <c r="A14" s="17" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C14" s="17">
         <v>0.0</v>
@@ -58638,21 +58642,21 @@
         <v>0</v>
       </c>
       <c r="K14" s="17" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="L14" s="18" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="M14" s="17"/>
       <c r="N14" s="17"/>
       <c r="O14" s="17"/>
     </row>
     <row r="15" ht="53.25" customHeight="1">
-      <c r="A15" s="109" t="s">
-        <v>692</v>
+      <c r="A15" s="108" t="s">
+        <v>693</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C15" s="17">
         <v>0.0</v>
@@ -58677,23 +58681,23 @@
         <v>0.4</v>
       </c>
       <c r="K15" s="17" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="L15" s="18" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="M15" s="18" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="N15" s="17"/>
       <c r="O15" s="17"/>
     </row>
     <row r="16" ht="53.25" customHeight="1">
-      <c r="A16" s="109" t="s">
-        <v>692</v>
-      </c>
-      <c r="B16" s="108" t="s">
-        <v>697</v>
+      <c r="A16" s="108" t="s">
+        <v>693</v>
+      </c>
+      <c r="B16" s="107" t="s">
+        <v>698</v>
       </c>
       <c r="C16" s="17"/>
       <c r="D16" s="18">
@@ -58720,11 +58724,11 @@
       <c r="O16" s="17"/>
     </row>
     <row r="17" ht="53.25" customHeight="1">
-      <c r="A17" s="109" t="s">
-        <v>692</v>
+      <c r="A17" s="108" t="s">
+        <v>693</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C17" s="17">
         <v>0.0</v>
@@ -58753,23 +58757,23 @@
         <v>0</v>
       </c>
       <c r="K17" s="17" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="L17" s="18" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="M17" s="18" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="N17" s="17"/>
       <c r="O17" s="17"/>
     </row>
     <row r="18" ht="53.25" customHeight="1">
       <c r="A18" s="17" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C18" s="17">
         <v>0.0</v>
@@ -58798,23 +58802,23 @@
         <v>0</v>
       </c>
       <c r="K18" s="17" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="L18" s="18" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="M18" s="18" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="N18" s="17"/>
       <c r="O18" s="17"/>
     </row>
     <row r="19" ht="53.25" customHeight="1">
       <c r="A19" s="17" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C19" s="17">
         <v>0.0</v>
@@ -58843,23 +58847,23 @@
         <v>0</v>
       </c>
       <c r="K19" s="17" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="L19" s="18" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="M19" s="18" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="N19" s="17"/>
       <c r="O19" s="17"/>
     </row>
     <row r="20" ht="53.25" customHeight="1">
       <c r="A20" s="17" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C20" s="17">
         <v>0.0</v>
@@ -58888,23 +58892,23 @@
         <v>0</v>
       </c>
       <c r="K20" s="17" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="L20" s="18" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="M20" s="18" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="N20" s="17"/>
       <c r="O20" s="17"/>
     </row>
     <row r="21" ht="53.25" customHeight="1">
       <c r="A21" s="20" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C21" s="17">
         <v>0.0</v>
@@ -58933,13 +58937,13 @@
         <v>0.3083333333</v>
       </c>
       <c r="K21" s="17" t="s">
-        <v>718</v>
-      </c>
-      <c r="L21" s="110" t="s">
         <v>719</v>
       </c>
+      <c r="L21" s="109" t="s">
+        <v>720</v>
+      </c>
       <c r="M21" s="18" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="N21" s="17"/>
       <c r="O21" s="17"/>
@@ -59937,7 +59941,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="39.63"/>
+    <col customWidth="1" min="1" max="1" width="59.5"/>
     <col customWidth="1" min="2" max="2" width="43.0"/>
     <col customWidth="1" min="3" max="3" width="19.88"/>
     <col customWidth="1" min="4" max="6" width="9.13"/>
@@ -59953,7 +59957,7 @@
   <sheetData>
     <row r="1" ht="32.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -60001,16 +60005,16 @@
         <v>4</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H4" s="11" t="s">
         <v>9</v>
@@ -60025,29 +60029,29 @@
         <v>12</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="5" ht="99.75" customHeight="1">
       <c r="A5" s="20" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>732</v>
-      </c>
-      <c r="D5" s="111">
+        <v>733</v>
+      </c>
+      <c r="D5" s="110">
         <v>0.0</v>
       </c>
       <c r="E5" s="18">
@@ -60071,26 +60075,26 @@
         <v>0.3787878788</v>
       </c>
       <c r="K5" s="17" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="L5" s="18" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="M5" s="18" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="N5" s="18"/>
       <c r="O5" s="17"/>
     </row>
     <row r="6" ht="99.75" customHeight="1">
       <c r="A6" s="20" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="D6" s="73">
         <v>0.0</v>
@@ -60114,28 +60118,28 @@
         <v>0.3333333333</v>
       </c>
       <c r="K6" s="17" t="s">
-        <v>738</v>
-      </c>
-      <c r="L6" s="112" t="s">
         <v>739</v>
       </c>
+      <c r="L6" s="111" t="s">
+        <v>740</v>
+      </c>
       <c r="M6" s="18" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="N6" s="17"/>
       <c r="O6" s="17"/>
     </row>
     <row r="7" ht="99.75" customHeight="1">
       <c r="A7" s="20" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>743</v>
-      </c>
-      <c r="D7" s="113">
+        <v>744</v>
+      </c>
+      <c r="D7" s="112">
         <v>0.0</v>
       </c>
       <c r="E7" s="19">
@@ -60158,27 +60162,27 @@
         <f t="shared" si="2"/>
         <v>0.12</v>
       </c>
-      <c r="K7" s="114" t="s">
-        <v>744</v>
+      <c r="K7" s="113" t="s">
+        <v>745</v>
       </c>
       <c r="L7" s="18" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="M7" s="18" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="N7" s="17"/>
       <c r="O7" s="17"/>
     </row>
     <row r="8" ht="99.75" customHeight="1">
       <c r="A8" s="20" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="D8" s="72">
         <v>0.0</v>
@@ -60204,26 +60208,26 @@
         <v>0.5</v>
       </c>
       <c r="K8" s="17" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="L8" s="18" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="M8" s="18" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="N8" s="17"/>
       <c r="O8" s="17"/>
     </row>
     <row r="9" ht="99.75" customHeight="1">
       <c r="A9" s="16" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B9" s="73" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C9" s="72" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="D9" s="73">
         <v>0.0</v>
@@ -60249,26 +60253,26 @@
         <v>1</v>
       </c>
       <c r="K9" s="73" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="L9" s="18" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="M9" s="18" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="N9" s="17"/>
       <c r="O9" s="17"/>
     </row>
     <row r="10" ht="99.75" customHeight="1">
       <c r="A10" s="16" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C10" s="72" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="D10" s="73"/>
       <c r="E10" s="73">
@@ -60291,27 +60295,27 @@
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
-      <c r="K10" s="114" t="s">
-        <v>762</v>
+      <c r="K10" s="113" t="s">
+        <v>763</v>
       </c>
       <c r="L10" s="18" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="M10" s="18" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="N10" s="17"/>
       <c r="O10" s="17"/>
     </row>
     <row r="11" ht="99.75" customHeight="1">
       <c r="A11" s="16" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D11" s="73">
         <v>0.0</v>
@@ -60337,26 +60341,26 @@
         <v>0.5</v>
       </c>
       <c r="K11" s="18" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="L11" s="18" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="M11" s="18" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="N11" s="17"/>
       <c r="O11" s="17"/>
     </row>
     <row r="12" ht="99.75" customHeight="1">
       <c r="A12" s="17" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="D12" s="17">
         <v>0.0</v>
@@ -60382,31 +60386,31 @@
         <v>0.5</v>
       </c>
       <c r="K12" s="17" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="L12" s="18" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="M12" s="18" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="N12" s="17"/>
       <c r="O12" s="17"/>
     </row>
     <row r="13" ht="99.75" customHeight="1">
       <c r="A13" s="17" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="D13" s="17">
         <v>0.0</v>
       </c>
-      <c r="E13" s="115">
+      <c r="E13" s="114">
         <v>0.02</v>
       </c>
       <c r="F13" s="17">
@@ -60415,7 +60419,7 @@
       <c r="G13" s="17">
         <v>0.0</v>
       </c>
-      <c r="H13" s="116">
+      <c r="H13" s="115">
         <f t="shared" si="1"/>
         <v>0.02</v>
       </c>
@@ -60427,26 +60431,26 @@
         <v>0.04</v>
       </c>
       <c r="K13" s="17" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="L13" s="18" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="M13" s="18" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="N13" s="17"/>
       <c r="O13" s="17"/>
     </row>
     <row r="14" ht="99.75" customHeight="1">
       <c r="A14" s="17" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="D14" s="17">
         <v>0.0</v>
@@ -60473,10 +60477,10 @@
       </c>
       <c r="K14" s="17"/>
       <c r="L14" s="18" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="M14" s="18" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="N14" s="17"/>
       <c r="O14" s="17"/>
@@ -60528,16 +60532,16 @@
         <v>4</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H17" s="11" t="s">
         <v>9</v>
@@ -60552,27 +60556,27 @@
         <v>12</v>
       </c>
       <c r="L17" s="11" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="M17" s="11" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="N17" s="11" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="O17" s="11" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
     </row>
     <row r="18" ht="99.75" customHeight="1">
       <c r="A18" s="20" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="D18" s="18">
         <v>0.0</v>
@@ -60598,26 +60602,26 @@
         <v>0.3333333333</v>
       </c>
       <c r="K18" s="17" t="s">
-        <v>798</v>
-      </c>
-      <c r="L18" s="112" t="s">
         <v>799</v>
       </c>
+      <c r="L18" s="111" t="s">
+        <v>800</v>
+      </c>
       <c r="M18" s="18" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="N18" s="17"/>
       <c r="O18" s="17"/>
     </row>
     <row r="19" ht="99.75" customHeight="1">
       <c r="A19" s="20" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="D19" s="17">
         <v>0.0</v>
@@ -60643,26 +60647,26 @@
         <v>0.5333333333</v>
       </c>
       <c r="K19" s="17" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="L19" s="18" t="s">
-        <v>805</v>
-      </c>
-      <c r="M19" s="112" t="s">
         <v>806</v>
+      </c>
+      <c r="M19" s="111" t="s">
+        <v>807</v>
       </c>
       <c r="N19" s="17"/>
       <c r="O19" s="17"/>
     </row>
     <row r="20" ht="99.75" customHeight="1">
       <c r="A20" s="20" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="D20" s="17">
         <v>0.0</v>
@@ -60688,26 +60692,26 @@
         <v>0.3225806452</v>
       </c>
       <c r="K20" s="17" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="L20" s="18" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="M20" s="18" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="N20" s="17"/>
       <c r="O20" s="17"/>
     </row>
     <row r="21" ht="99.75" customHeight="1">
       <c r="A21" s="20" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="D21" s="18">
         <v>5.0</v>
@@ -60733,26 +60737,26 @@
         <v>0.5483870968</v>
       </c>
       <c r="K21" s="17" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="L21" s="18" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="M21" s="18" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="N21" s="17"/>
       <c r="O21" s="17"/>
     </row>
     <row r="22" ht="99.75" customHeight="1">
       <c r="A22" s="20" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B22" s="73" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C22" s="72" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="D22" s="73">
         <v>5.0</v>
@@ -60778,26 +60782,26 @@
         <v>0.6</v>
       </c>
       <c r="K22" s="73" t="s">
-        <v>822</v>
-      </c>
-      <c r="L22" s="112" t="s">
         <v>823</v>
       </c>
-      <c r="M22" s="112" t="s">
+      <c r="L22" s="111" t="s">
         <v>824</v>
+      </c>
+      <c r="M22" s="111" t="s">
+        <v>825</v>
       </c>
       <c r="N22" s="17"/>
       <c r="O22" s="17"/>
     </row>
     <row r="23" ht="99.75" customHeight="1">
       <c r="A23" s="20" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="D23" s="72">
         <v>0.0</v>
@@ -60822,29 +60826,29 @@
         <f t="shared" si="5"/>
         <v>0.3</v>
       </c>
-      <c r="K23" s="114" t="s">
-        <v>828</v>
+      <c r="K23" s="113" t="s">
+        <v>829</v>
       </c>
       <c r="L23" s="22" t="s">
-        <v>829</v>
-      </c>
-      <c r="M23" s="112" t="s">
         <v>830</v>
+      </c>
+      <c r="M23" s="111" t="s">
+        <v>831</v>
       </c>
       <c r="N23" s="17"/>
       <c r="O23" s="17"/>
     </row>
     <row r="24" ht="99.75" customHeight="1">
       <c r="A24" s="20" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>833</v>
-      </c>
-      <c r="D24" s="117">
+        <v>834</v>
+      </c>
+      <c r="D24" s="116">
         <v>0.0</v>
       </c>
       <c r="E24" s="73">
@@ -60856,11 +60860,11 @@
       <c r="G24" s="72">
         <v>0.0</v>
       </c>
-      <c r="H24" s="118">
+      <c r="H24" s="117">
         <f t="shared" si="3"/>
         <v>0.0018</v>
       </c>
-      <c r="I24" s="119">
+      <c r="I24" s="118">
         <v>0.18</v>
       </c>
       <c r="J24" s="34">
@@ -60868,26 +60872,26 @@
         <v>0.01</v>
       </c>
       <c r="K24" s="17" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="L24" s="18" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="M24" s="18" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="N24" s="17"/>
       <c r="O24" s="17"/>
     </row>
     <row r="25" ht="99.75" customHeight="1">
       <c r="A25" s="17" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="D25" s="17">
         <v>0.0</v>
@@ -60912,27 +60916,27 @@
         <f t="shared" si="5"/>
         <v>1.2</v>
       </c>
-      <c r="K25" s="120" t="s">
-        <v>840</v>
+      <c r="K25" s="119" t="s">
+        <v>841</v>
       </c>
       <c r="L25" s="22" t="s">
-        <v>841</v>
-      </c>
-      <c r="M25" s="112" t="s">
         <v>842</v>
+      </c>
+      <c r="M25" s="111" t="s">
+        <v>843</v>
       </c>
       <c r="N25" s="17"/>
       <c r="O25" s="17"/>
     </row>
     <row r="26" ht="99.75" customHeight="1">
       <c r="A26" s="20" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="D26" s="17">
         <v>0.0</v>
@@ -60958,26 +60962,26 @@
         <v>0.01</v>
       </c>
       <c r="K26" s="17" t="s">
-        <v>846</v>
-      </c>
-      <c r="L26" s="112" t="s">
         <v>847</v>
       </c>
-      <c r="M26" s="112" t="s">
+      <c r="L26" s="111" t="s">
         <v>848</v>
+      </c>
+      <c r="M26" s="111" t="s">
+        <v>849</v>
       </c>
       <c r="N26" s="17"/>
       <c r="O26" s="17"/>
     </row>
     <row r="27" ht="99.75" customHeight="1">
       <c r="A27" s="20" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="D27" s="17">
         <v>0.0</v>
@@ -61003,26 +61007,26 @@
         <v>1.714285714</v>
       </c>
       <c r="K27" s="18" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="L27" s="44" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="M27" s="18" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="N27" s="17"/>
       <c r="O27" s="17"/>
     </row>
     <row r="28" ht="99.75" customHeight="1">
       <c r="A28" s="20" t="s">
-        <v>843</v>
-      </c>
-      <c r="B28" s="112" t="s">
-        <v>854</v>
+        <v>844</v>
+      </c>
+      <c r="B28" s="111" t="s">
+        <v>855</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="D28" s="19">
         <v>0.0</v>
@@ -61047,27 +61051,27 @@
         <f t="shared" si="5"/>
         <v>0.6666666667</v>
       </c>
-      <c r="K28" s="121" t="s">
-        <v>855</v>
-      </c>
-      <c r="L28" s="112" t="s">
+      <c r="K28" s="120" t="s">
         <v>856</v>
       </c>
-      <c r="M28" s="122" t="s">
+      <c r="L28" s="111" t="s">
         <v>857</v>
       </c>
-      <c r="N28" s="112"/>
-      <c r="O28" s="112"/>
+      <c r="M28" s="121" t="s">
+        <v>858</v>
+      </c>
+      <c r="N28" s="111"/>
+      <c r="O28" s="111"/>
     </row>
     <row r="29" ht="99.75" customHeight="1">
       <c r="A29" s="20" t="s">
-        <v>843</v>
-      </c>
-      <c r="B29" s="123" t="s">
-        <v>858</v>
+        <v>844</v>
+      </c>
+      <c r="B29" s="122" t="s">
+        <v>859</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="D29" s="17">
         <v>0.0</v>
@@ -61092,12 +61096,12 @@
         <f t="shared" si="5"/>
         <v>0.1666666667</v>
       </c>
-      <c r="K29" s="121" t="s">
-        <v>859</v>
+      <c r="K29" s="120" t="s">
+        <v>860</v>
       </c>
       <c r="L29" s="50"/>
-      <c r="M29" s="112" t="s">
-        <v>860</v>
+      <c r="M29" s="111" t="s">
+        <v>861</v>
       </c>
       <c r="N29" s="50"/>
       <c r="O29" s="50"/>
